--- a/planning/store_planning_model.xlsx
+++ b/planning/store_planning_model.xlsx
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="258">
   <si>
     <t xml:space="preserve">Store planning model</t>
   </si>
@@ -183,7 +183,7 @@
     <t xml:space="preserve">$ per sq ft</t>
   </si>
   <si>
-    <t xml:space="preserve">Construction, equipment, fixtures.</t>
+    <t xml:space="preserve">Construction, equipment and fixtures, including a full cafe and hot bar.</t>
   </si>
   <si>
     <t xml:space="preserve">Store running costs</t>
@@ -204,73 +204,79 @@
     <t xml:space="preserve">$ per sq ft per year</t>
   </si>
   <si>
+    <t xml:space="preserve">Not in the data. A premium street-level location.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other operating costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Card fees, utilities, supplies, repairs, local marketing. Not in the data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales vs today's run-rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0% means the next 13 weeks sell at the last 30 days' pace.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same in every scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flagship size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sq ft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Store sizes are not in the data. Sized as a boutique grocer and cafe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Store 2 size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Store 3 size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New store size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The same format as the flagship.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opening costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hiring, training, launch marketing and the first stock.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labor floor while a store ramps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of mature labor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A new store can't cut staff in line with lower early sales.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head office costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finance, buying, marketing, leadership.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash in the bank today</t>
+  </si>
+  <si>
     <t xml:space="preserve">Not in the data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other operating costs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Card fees, utilities, supplies, repairs, local marketing. Not in the data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cash forecast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sales vs today's run-rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0% means the next 13 weeks sell at the last 30 days' pace.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same in every scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flagship size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sq ft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Store sizes are not in the data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Store 2 size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Store 3 size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New store size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opening costs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hiring, training, launch marketing and the first stock.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Labor floor while a store ramps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% of mature labor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A new store can't cut staff in line with lower early sales.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head office costs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finance, buying, marketing, leadership.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cash in the bank today</t>
   </si>
   <si>
     <t xml:space="preserve">Cash cushion to keep</t>
@@ -1874,187 +1880,187 @@
                 <c:formatCode>\$#,##0,\K;[RED]"($"#,##0,"K)";\-</c:formatCode>
                 <c:ptCount val="61"/>
                 <c:pt idx="0">
-                  <c:v>-2350000</c:v>
+                  <c:v>-1995000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-2354867.78018934</c:v>
+                  <c:v>-1977551.67028401</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-2355016.36689685</c:v>
+                  <c:v>-1953024.55034527</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-2350445.76012253</c:v>
+                  <c:v>-1921418.6401838</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-2341155.95986639</c:v>
+                  <c:v>-1882733.93979958</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-2327146.96612842</c:v>
+                  <c:v>-1836970.44919263</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-2308418.77890862</c:v>
+                  <c:v>-1784128.16836293</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-2284971.398207</c:v>
+                  <c:v>-1724207.09731049</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-2256804.82402354</c:v>
+                  <c:v>-1657207.23603532</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-2223919.05635827</c:v>
+                  <c:v>-1583128.5845374</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-2186314.09521116</c:v>
+                  <c:v>-1501971.14281674</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-2143989.94058223</c:v>
+                  <c:v>-1413734.91087334</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-2097831.09642278</c:v>
+                  <c:v>-1319746.64463416</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-2049311.73598498</c:v>
+                  <c:v>-1222217.60397747</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1998431.85926885</c:v>
+                  <c:v>-1121147.78890327</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1945191.46627437</c:v>
+                  <c:v>-1016537.19941156</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-1889590.55700155</c:v>
+                  <c:v>-908385.835502331</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1831629.1314504</c:v>
+                  <c:v>-796693.697175594</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1771307.1896209</c:v>
+                  <c:v>-681460.784431345</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-1710985.2477914</c:v>
+                  <c:v>-566227.871687096</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-1650663.3059619</c:v>
+                  <c:v>-450994.958942847</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-1590341.3641324</c:v>
+                  <c:v>-335762.046198598</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-1530019.4223029</c:v>
+                  <c:v>-220529.133454349</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-1469697.4804734</c:v>
+                  <c:v>-105296.2207101</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-1409375.5386439</c:v>
+                  <c:v>9936.69203414887</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-1349053.5968144</c:v>
+                  <c:v>125169.604778398</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-1288731.6549849</c:v>
+                  <c:v>240402.517522647</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-1228409.7131554</c:v>
+                  <c:v>355635.430266896</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-1168087.7713259</c:v>
+                  <c:v>470868.343011145</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-1107765.8294964</c:v>
+                  <c:v>586101.255755394</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-1047443.88766691</c:v>
+                  <c:v>701334.168499643</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>-987121.945837406</c:v>
+                  <c:v>816567.081243892</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-926800.004007907</c:v>
+                  <c:v>931799.993988141</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-866478.062178408</c:v>
+                  <c:v>1047032.90673239</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>-806156.120348909</c:v>
+                  <c:v>1162265.81947664</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>-745834.17851941</c:v>
+                  <c:v>1277498.73222089</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-685512.23668991</c:v>
+                  <c:v>1392731.64496514</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>-625190.294860411</c:v>
+                  <c:v>1507964.55770939</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>-564868.353030912</c:v>
+                  <c:v>1623197.47045363</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>-504546.411201413</c:v>
+                  <c:v>1738430.38319788</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>-444224.469371913</c:v>
+                  <c:v>1853663.29594213</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>-383902.527542414</c:v>
+                  <c:v>1968896.20868638</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>-323580.585712915</c:v>
+                  <c:v>2084129.12143063</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>-263258.643883416</c:v>
+                  <c:v>2199362.03417488</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>-202936.702053916</c:v>
+                  <c:v>2314594.94691913</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>-142614.760224417</c:v>
+                  <c:v>2429827.85966338</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>-82292.8183949179</c:v>
+                  <c:v>2545060.77240763</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>-21970.8765654186</c:v>
+                  <c:v>2660293.68515187</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>38351.0652640806</c:v>
+                  <c:v>2775526.59789612</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>98673.0070935799</c:v>
+                  <c:v>2890759.51064037</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>158994.948923079</c:v>
+                  <c:v>3005992.42338462</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>219316.890752578</c:v>
+                  <c:v>3121225.33612887</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>279638.832582078</c:v>
+                  <c:v>3236458.24887312</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>339960.774411577</c:v>
+                  <c:v>3351691.16161737</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>400282.716241076</c:v>
+                  <c:v>3466924.07436162</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>460604.658070575</c:v>
+                  <c:v>3582156.98710586</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>520926.599900075</c:v>
+                  <c:v>3697389.89985011</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>581248.541729574</c:v>
+                  <c:v>3812622.81259436</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>641570.483559073</c:v>
+                  <c:v>3927855.72533861</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>701892.425388572</c:v>
+                  <c:v>4043088.63808286</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>762214.367218072</c:v>
+                  <c:v>4158321.55082711</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2069,11 +2075,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="91608594"/>
-        <c:axId val="15676903"/>
+        <c:axId val="96542646"/>
+        <c:axId val="75429530"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="91608594"/>
+        <c:axId val="96542646"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2139,7 +2145,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15676903"/>
+        <c:crossAx val="75429530"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2147,7 +2153,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="15676903"/>
+        <c:axId val="75429530"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2190,7 +2196,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91608594"/>
+        <c:crossAx val="96542646"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2350,43 +2356,43 @@
                 <c:formatCode>\$#,##0,\K;[RED]"($"#,##0,"K)";\-</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>611553.192248345</c:v>
+                  <c:v>666303.192248345</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>744963.804998198</c:v>
+                  <c:v>799713.804998198</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>734250.647872111</c:v>
+                  <c:v>789000.647872111</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>857870.56626951</c:v>
+                  <c:v>912620.56626951</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>467974.342902395</c:v>
+                  <c:v>612974.342902395</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>353849.626690761</c:v>
+                  <c:v>534349.626690761</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>100491.509167962</c:v>
+                  <c:v>316491.509167962</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-12930.3002815043</c:v>
+                  <c:v>238569.699718496</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-266288.417804304</c:v>
+                  <c:v>20711.5821956963</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-514710.22725377</c:v>
+                  <c:v>-137460.22725377</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-768068.344776569</c:v>
+                  <c:v>-355318.344776569</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-881490.154226035</c:v>
+                  <c:v>-433240.154226035</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1134848.27174883</c:v>
+                  <c:v>-651098.271748835</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2538,11 +2544,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="76177931"/>
-        <c:axId val="6816990"/>
+        <c:axId val="89365619"/>
+        <c:axId val="15001668"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="76177931"/>
+        <c:axId val="89365619"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2608,7 +2614,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6816990"/>
+        <c:crossAx val="15001668"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2616,7 +2622,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="6816990"/>
+        <c:axId val="15001668"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2659,7 +2665,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76177931"/>
+        <c:crossAx val="89365619"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2832,11 +2838,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="31144829"/>
-        <c:axId val="73250544"/>
+        <c:axId val="62839655"/>
+        <c:axId val="69096958"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="31144829"/>
+        <c:axId val="62839655"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2869,7 +2875,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73250544"/>
+        <c:crossAx val="69096958"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2877,7 +2883,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="73250544"/>
+        <c:axId val="69096958"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2920,7 +2926,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31144829"/>
+        <c:crossAx val="62839655"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3994,12 +4000,12 @@
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="str">
         <f aca="false">IF(ISNUMBER(ns_payback),ns_payback&amp;" months","Over 60 months")</f>
-        <v>48 months</v>
+        <v>24 months</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="n">
         <f aca="false">cash_funding</f>
-        <v>1384848.27174883</v>
+        <v>901098.271748835</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="n">
@@ -4016,12 +4022,12 @@
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="str">
         <f aca="false">"on an investment of "&amp;TEXT(ns_invest,"$#,##0")</f>
-        <v>on an investment of $2,350,000</v>
+        <v>on an investment of $1,995,000</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7" t="str">
         <f aca="false">"lowest cash: "&amp;TEXT(cash_low,"$#,##0;-$#,##0")</f>
-        <v>lowest cash: -$1,134,848</v>
+        <v>lowest cash: -$651,098</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="7" t="str">
@@ -4051,13 +4057,13 @@
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="str">
         <f aca="false">"A new store costs "&amp;TEXT(ns_invest,"$#,##0")&amp;" and "&amp;IF(ISNUMBER(ns_payback),"pays back in "&amp;ns_payback&amp;" months.","does not pay back within 5 years.")</f>
-        <v>A new store costs $2,350,000 and pays back in 48 months.</v>
+        <v>A new store costs $1,995,000 and pays back in 24 months.</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="str">
         <f aca="false">IF(build_start=0,"No new store build is planned in the next 13 weeks.",IF(cash_funding&gt;0,"Starting the build in week "&amp;build_start&amp;" needs about "&amp;TEXT(cash_funding,"$#,##0")&amp;" of outside funding to keep "&amp;TEXT(cash_cushion,"$#,##0")&amp;" in the bank.","The build starting in week "&amp;build_start&amp;" can be paid from cash, staying above the "&amp;TEXT(cash_cushion,"$#,##0")&amp;" cushion."))</f>
-        <v>Starting the build in week 5 needs about $1,384,848 of outside funding to keep $250,000 in the bank.</v>
+        <v>Starting the build in week 5 needs about $901,098 of outside funding to keep $250,000 in the bank.</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4267,7 +4273,7 @@
       </c>
       <c r="G9" s="21" t="n">
         <f aca="false">IF(s1_per_day=0,0,(s3_per_day/sqft_s3)/(s1_per_day/sqft_s1))</f>
-        <v>0.607548402810125</v>
+        <v>0.594891144418247</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>30</v>
@@ -4306,16 +4312,16 @@
       </c>
       <c r="C11" s="24" t="n">
         <f aca="false">INDEX(D11:F11,MATCH(scenario,$D$6:$F$6,0))</f>
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E11" s="25" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="F11" s="25" t="n">
-        <v>300</v>
+        <v>425</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>36</v>
@@ -4366,16 +4372,16 @@
       </c>
       <c r="C15" s="24" t="n">
         <f aca="false">INDEX(D15:F15,MATCH(scenario,$D$6:$F$6,0))</f>
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E15" s="25" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="F15" s="25" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>43</v>
@@ -4461,7 +4467,7 @@
         <v>52</v>
       </c>
       <c r="C22" s="30" t="n">
-        <v>12000</v>
+        <v>4700</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>53</v>
@@ -4475,7 +4481,7 @@
         <v>52</v>
       </c>
       <c r="C23" s="30" t="n">
-        <v>8500</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4486,7 +4492,7 @@
         <v>52</v>
       </c>
       <c r="C24" s="30" t="n">
-        <v>6500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4497,40 +4503,43 @@
         <v>52</v>
       </c>
       <c r="C25" s="30" t="n">
-        <v>8000</v>
+        <v>4700</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C26" s="31" t="n">
         <v>350000</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C27" s="32" t="n">
         <v>0.85</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>39</v>
@@ -4539,57 +4548,57 @@
         <v>0.05</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C29" s="31" t="n">
         <v>750000</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C30" s="31" t="n">
         <v>250000</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C31" s="34" t="n">
         <v>5</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C32" s="34" t="n">
         <v>10</v>
@@ -4597,7 +4606,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -4627,7 +4636,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4638,7 +4647,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -4648,20 +4657,20 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B5" s="35" t="n">
         <f aca="false">sqft_new</f>
-        <v>8000</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B6" s="36" t="n">
         <f aca="false">IF(sqft_s1=0,0,flag_runrate/sqft_s1)</f>
-        <v>791.398272222222</v>
+        <v>2020.59133333333</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4675,16 +4684,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B8" s="36" t="n">
         <f aca="false">B5*B6*B7</f>
-        <v>6331186.17777778</v>
+        <v>9496779.26666667</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B9" s="37" t="n">
         <f aca="false">gm_actual</f>
@@ -4697,12 +4706,12 @@
       </c>
       <c r="B10" s="36" t="n">
         <f aca="false">B5*buildout_psf</f>
-        <v>2000000</v>
+        <v>1645000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B11" s="38" t="n">
         <f aca="false">opening_costs</f>
@@ -4711,16 +4720,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B12" s="24" t="n">
         <f aca="false">B10+B11</f>
-        <v>2350000</v>
+        <v>1995000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -4730,43 +4739,43 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B15" s="39" t="n">
         <f aca="false">IF(MIN($D56:$BK56)&gt;60,"Over 60",MIN($D56:$BK56))</f>
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B16" s="40" t="n">
         <f aca="false">D29</f>
-        <v>723863.301953991</v>
+        <v>1382794.95293099</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B17" s="41" t="n">
         <f aca="false">IF(ns_invest=0,0,D29/ns_invest)</f>
-        <v>0.308026937001698</v>
+        <v>0.693130302221046</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B18" s="41" t="n">
         <f aca="false">IF(ns_mature_sales=0,0,ns_gm-waste_actual-labor_pct-other_pct-sqft_new*rent_psf/ns_mature_sales)</f>
-        <v>0.114332967255761</v>
+        <v>0.145606727723424</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -4793,102 +4802,102 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B23" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,B$22,$D46:$BK46)</f>
-        <v>4618041.68261438</v>
+        <v>6927062.52392157</v>
       </c>
       <c r="C23" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,C$22,$D46:$BK46)</f>
-        <v>6144974.81960784</v>
+        <v>9217462.22941176</v>
       </c>
       <c r="D23" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,D$22,$D46:$BK46)</f>
-        <v>6331186.17777778</v>
+        <v>9496779.26666667</v>
       </c>
       <c r="E23" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,E$22,$D46:$BK46)</f>
-        <v>6331186.17777778</v>
+        <v>9496779.26666667</v>
       </c>
       <c r="F23" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,F$22,$D46:$BK46)</f>
-        <v>6331186.17777778</v>
+        <v>9496779.26666667</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B24" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,B$22,$D47:$BK47)</f>
-        <v>2211730.74260497</v>
+        <v>3317596.11390746</v>
       </c>
       <c r="C24" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,C$22,$D47:$BK47)</f>
-        <v>2943028.81072436</v>
+        <v>4414543.21608654</v>
       </c>
       <c r="D24" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,D$22,$D47:$BK47)</f>
-        <v>3032211.50195843</v>
+        <v>4548317.25293764</v>
       </c>
       <c r="E24" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,E$22,$D47:$BK47)</f>
-        <v>3032211.50195843</v>
+        <v>4548317.25293764</v>
       </c>
       <c r="F24" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,F$22,$D47:$BK47)</f>
-        <v>3032211.50195843</v>
+        <v>4548317.25293764</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B25" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,B$22,$D48:$BK48)</f>
-        <v>86747.4327561781</v>
+        <v>130121.149134267</v>
       </c>
       <c r="C25" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,C$22,$D48:$BK48)</f>
-        <v>115430.051651366</v>
+        <v>173145.077477049</v>
       </c>
       <c r="D25" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,D$22,$D48:$BK48)</f>
-        <v>118927.932004438</v>
+        <v>178391.898006657</v>
       </c>
       <c r="E25" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,E$22,$D48:$BK48)</f>
-        <v>118927.932004438</v>
+        <v>178391.898006657</v>
       </c>
       <c r="F25" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,F$22,$D48:$BK48)</f>
-        <v>118927.932004438</v>
+        <v>178391.898006657</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B26" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,B$22,$D49:$BK49)</f>
-        <v>1023371.07166242</v>
+        <v>1535056.60749363</v>
       </c>
       <c r="C26" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,C$22,$D49:$BK49)</f>
-        <v>1167545.21572549</v>
+        <v>1751317.82358824</v>
       </c>
       <c r="D26" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,D$22,$D49:$BK49)</f>
-        <v>1202925.37377778</v>
+        <v>1804388.06066667</v>
       </c>
       <c r="E26" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,E$22,$D49:$BK49)</f>
-        <v>1202925.37377778</v>
+        <v>1804388.06066667</v>
       </c>
       <c r="F26" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,F$22,$D49:$BK49)</f>
-        <v>1202925.37377778</v>
+        <v>1804388.06066667</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4897,23 +4906,23 @@
       </c>
       <c r="B27" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,B$22,$D50:$BK50)</f>
-        <v>480000</v>
+        <v>423000</v>
       </c>
       <c r="C27" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,C$22,$D50:$BK50)</f>
-        <v>480000</v>
+        <v>423000</v>
       </c>
       <c r="D27" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,D$22,$D50:$BK50)</f>
-        <v>480000</v>
+        <v>423000</v>
       </c>
       <c r="E27" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,E$22,$D50:$BK50)</f>
-        <v>480000</v>
+        <v>423000</v>
       </c>
       <c r="F27" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,F$22,$D50:$BK50)</f>
-        <v>480000</v>
+        <v>423000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4922,103 +4931,103 @@
       </c>
       <c r="B28" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,B$22,$D51:$BK51)</f>
-        <v>369443.33460915</v>
+        <v>554165.001913725</v>
       </c>
       <c r="C28" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,C$22,$D51:$BK51)</f>
-        <v>491597.985568627</v>
+        <v>737396.978352941</v>
       </c>
       <c r="D28" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,D$22,$D51:$BK51)</f>
-        <v>506494.894222222</v>
+        <v>759742.341333333</v>
       </c>
       <c r="E28" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,E$22,$D51:$BK51)</f>
-        <v>506494.894222222</v>
+        <v>759742.341333333</v>
       </c>
       <c r="F28" s="36" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,F$22,$D51:$BK51)</f>
-        <v>506494.894222222</v>
+        <v>759742.341333333</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="43" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B29" s="44" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,B$22,$D52:$BK52)</f>
-        <v>252168.903577225</v>
+        <v>675253.355365838</v>
       </c>
       <c r="C29" s="44" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,C$22,$D52:$BK52)</f>
-        <v>688455.557778874</v>
+        <v>1329683.33666831</v>
       </c>
       <c r="D29" s="44" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,D$22,$D52:$BK52)</f>
-        <v>723863.301953991</v>
+        <v>1382794.95293099</v>
       </c>
       <c r="E29" s="44" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,E$22,$D52:$BK52)</f>
-        <v>723863.301953991</v>
+        <v>1382794.95293099</v>
       </c>
       <c r="F29" s="44" t="n">
         <f aca="false">SUMIF($D$44:$BK$44,F$22,$D52:$BK52)</f>
-        <v>723863.301953991</v>
+        <v>1382794.95293099</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B30" s="45" t="n">
         <f aca="false">IF(B23=0,0,B29/B23)</f>
-        <v>0.0546051596993093</v>
+        <v>0.0974804764694922</v>
       </c>
       <c r="C30" s="45" t="n">
         <f aca="false">IF(C23=0,0,C29/C23)</f>
-        <v>0.112035537652994</v>
+        <v>0.144256987831798</v>
       </c>
       <c r="D30" s="45" t="n">
         <f aca="false">IF(D23=0,0,D29/D23)</f>
-        <v>0.114332967255761</v>
+        <v>0.145606727723424</v>
       </c>
       <c r="E30" s="45" t="n">
         <f aca="false">IF(E23=0,0,E29/E23)</f>
-        <v>0.114332967255761</v>
+        <v>0.145606727723424</v>
       </c>
       <c r="F30" s="45" t="n">
         <f aca="false">IF(F23=0,0,F29/F23)</f>
-        <v>0.114332967255761</v>
+        <v>0.145606727723424</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B31" s="36" t="n">
         <f aca="false">INDEX($D55:$BK55,MATCH(B22*12,$D$43:$BK$43,0))</f>
-        <v>-2097831.09642278</v>
+        <v>-1319746.64463416</v>
       </c>
       <c r="C31" s="36" t="n">
         <f aca="false">INDEX($D55:$BK55,MATCH(C22*12,$D$43:$BK$43,0))</f>
-        <v>-1409375.5386439</v>
+        <v>9936.69203414887</v>
       </c>
       <c r="D31" s="36" t="n">
         <f aca="false">INDEX($D55:$BK55,MATCH(D22*12,$D$43:$BK$43,0))</f>
-        <v>-685512.23668991</v>
+        <v>1392731.64496514</v>
       </c>
       <c r="E31" s="36" t="n">
         <f aca="false">INDEX($D55:$BK55,MATCH(E22*12,$D$43:$BK$43,0))</f>
-        <v>38351.0652640806</v>
+        <v>2775526.59789612</v>
       </c>
       <c r="F31" s="36" t="n">
         <f aca="false">INDEX($D55:$BK55,MATCH(F22*12,$D$43:$BK$43,0))</f>
-        <v>762214.367218072</v>
+        <v>4158321.55082711</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -5028,12 +5037,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B35" s="46" t="n">
         <f aca="false">ns_gm-0.02</f>
@@ -5063,23 +5072,23 @@
       </c>
       <c r="B36" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A36*(B$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>381791.662718749</v>
+        <v>869687.494078123</v>
       </c>
       <c r="C36" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A36*(C$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>432441.152140971</v>
+        <v>945661.728211456</v>
       </c>
       <c r="D36" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A36*(D$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>483090.641563193</v>
+        <v>1021635.96234479</v>
       </c>
       <c r="E36" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A36*(E$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>533740.130985415</v>
+        <v>1097610.19647812</v>
       </c>
       <c r="F36" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A36*(F$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>584389.620407638</v>
+        <v>1173584.43061146</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5089,23 +5098,23 @@
       </c>
       <c r="B37" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A37*(B$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>489515.620558592</v>
+        <v>1031273.43083789</v>
       </c>
       <c r="C37" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A37*(C$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>546496.296158592</v>
+        <v>1116744.44423789</v>
       </c>
       <c r="D37" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A37*(D$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>603476.971758592</v>
+        <v>1202215.45763789</v>
       </c>
       <c r="E37" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A37*(E$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>660457.647358592</v>
+        <v>1287686.47103789</v>
       </c>
       <c r="F37" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A37*(F$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>717438.322958592</v>
+        <v>1373157.48443789</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5115,23 +5124,23 @@
       </c>
       <c r="B38" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A38*(B$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>597239.578398436</v>
+        <v>1192859.36759765</v>
       </c>
       <c r="C38" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A38*(C$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>660551.440176213</v>
+        <v>1287827.16026432</v>
       </c>
       <c r="D38" s="49" t="n">
         <f aca="false">$B$5*$B$6*$A38*(D$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>723863.301953991</v>
+        <v>1382794.95293099</v>
       </c>
       <c r="E38" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A38*(E$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>787175.163731769</v>
+        <v>1477762.74559765</v>
       </c>
       <c r="F38" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A38*(F$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>850487.025509547</v>
+        <v>1572730.53826432</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5141,23 +5150,23 @@
       </c>
       <c r="B39" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A39*(B$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>704963.536238279</v>
+        <v>1354445.30435742</v>
       </c>
       <c r="C39" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A39*(C$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>774606.584193835</v>
+        <v>1458909.87629075</v>
       </c>
       <c r="D39" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A39*(D$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>844249.63214939</v>
+        <v>1563374.44822409</v>
       </c>
       <c r="E39" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A39*(E$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>913892.680104946</v>
+        <v>1667839.02015742</v>
       </c>
       <c r="F39" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A39*(F$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>983535.728060502</v>
+        <v>1772303.59209075</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5167,28 +5176,28 @@
       </c>
       <c r="B40" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A40*(B$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>812687.494078123</v>
+        <v>1516031.24111718</v>
       </c>
       <c r="C40" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A40*(C$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>888661.728211456</v>
+        <v>1629992.59231718</v>
       </c>
       <c r="D40" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A40*(D$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>964635.962344789</v>
+        <v>1743953.94351718</v>
       </c>
       <c r="E40" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A40*(E$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>1040610.19647812</v>
+        <v>1857915.29471718</v>
       </c>
       <c r="F40" s="48" t="n">
         <f aca="false">$B$5*$B$6*$A40*(F$35-waste_actual-labor_pct-other_pct)-$B$5*rent_psf</f>
-        <v>1116584.43061146</v>
+        <v>1971876.64591718</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B42" s="11"/>
       <c r="C42" s="11"/>
@@ -5198,7 +5207,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C43" s="34" t="n">
         <v>0</v>
@@ -5446,7 +5455,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C44" s="51" t="n">
         <v>0</v>
@@ -5694,7 +5703,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D45" s="53" t="n">
         <f aca="false">IF(D$43&gt;=ramp_months,1,ramp_start+(1-ramp_start)*(D$43-1)/MAX(1,ramp_months-1))</f>
@@ -5939,982 +5948,982 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*D45</f>
-        <v>316559.308888889</v>
+        <v>474838.963333333</v>
       </c>
       <c r="E46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*E45</f>
-        <v>328973.399433551</v>
+        <v>493460.099150327</v>
       </c>
       <c r="F46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*F45</f>
-        <v>341387.489978213</v>
+        <v>512081.23496732</v>
       </c>
       <c r="G46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*G45</f>
-        <v>353801.580522876</v>
+        <v>530702.370784314</v>
       </c>
       <c r="H46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*H45</f>
-        <v>366215.671067538</v>
+        <v>549323.506601307</v>
       </c>
       <c r="I46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*I45</f>
-        <v>378629.7616122</v>
+        <v>567944.642418301</v>
       </c>
       <c r="J46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*J45</f>
-        <v>391043.852156863</v>
+        <v>586565.778235294</v>
       </c>
       <c r="K46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*K45</f>
-        <v>403457.942701525</v>
+        <v>605186.914052288</v>
       </c>
       <c r="L46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*L45</f>
-        <v>415872.033246187</v>
+        <v>623808.049869281</v>
       </c>
       <c r="M46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*M45</f>
-        <v>428286.12379085</v>
+        <v>642429.185686274</v>
       </c>
       <c r="N46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*N45</f>
-        <v>440700.214335512</v>
+        <v>661050.321503268</v>
       </c>
       <c r="O46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*O45</f>
-        <v>453114.304880174</v>
+        <v>679671.457320261</v>
       </c>
       <c r="P46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*P45</f>
-        <v>465528.395424837</v>
+        <v>698292.593137255</v>
       </c>
       <c r="Q46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*Q45</f>
-        <v>477942.485969499</v>
+        <v>716913.728954248</v>
       </c>
       <c r="R46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*R45</f>
-        <v>490356.576514161</v>
+        <v>735534.864771242</v>
       </c>
       <c r="S46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*S45</f>
-        <v>502770.667058823</v>
+        <v>754156.000588235</v>
       </c>
       <c r="T46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*T45</f>
-        <v>515184.757603486</v>
+        <v>772777.136405229</v>
       </c>
       <c r="U46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*U45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="V46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*V45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="W46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*W45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="X46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*X45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="Y46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*Y45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="Z46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*Z45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AA46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AA45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AB46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AB45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AC46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AC45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AD46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AD45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AE46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AE45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AF46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AF45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AG46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AG45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AH46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AH45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AI46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AI45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AJ46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AJ45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AK46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AK45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AL46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AL45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AM46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AM45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AN46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AN45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AO46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AO45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AP46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AP45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AQ46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AQ45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AR46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AR45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AS46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AS45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AT46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AT45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AU46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AU45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AV46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AV45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AW46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AW45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AX46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AX45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AY46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AY45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="AZ46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*AZ45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="BA46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*BA45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="BB46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*BB45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="BC46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*BC45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="BD46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*BD45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="BE46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*BE45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="BF46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*BF45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="BG46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*BG45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="BH46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*BH45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="BI46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*BI45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="BJ46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*BJ45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
       <c r="BK46" s="48" t="n">
         <f aca="false">ns_mature_sales/12*BK45</f>
-        <v>527598.848148148</v>
+        <v>791398.272222222</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D47" s="48" t="n">
         <f aca="false">D46*ns_gm</f>
-        <v>151610.575097921</v>
+        <v>227415.862646882</v>
       </c>
       <c r="E47" s="48" t="n">
         <f aca="false">E46*ns_gm</f>
-        <v>157556.08784686</v>
+        <v>236334.131770289</v>
       </c>
       <c r="F47" s="48" t="n">
         <f aca="false">F46*ns_gm</f>
-        <v>163501.600595798</v>
+        <v>245252.400893696</v>
       </c>
       <c r="G47" s="48" t="n">
         <f aca="false">G46*ns_gm</f>
-        <v>169447.113344736</v>
+        <v>254170.670017104</v>
       </c>
       <c r="H47" s="48" t="n">
         <f aca="false">H46*ns_gm</f>
-        <v>175392.626093674</v>
+        <v>263088.939140511</v>
       </c>
       <c r="I47" s="48" t="n">
         <f aca="false">I46*ns_gm</f>
-        <v>181338.138842612</v>
+        <v>272007.208263918</v>
       </c>
       <c r="J47" s="48" t="n">
         <f aca="false">J46*ns_gm</f>
-        <v>187283.65159155</v>
+        <v>280925.477387325</v>
       </c>
       <c r="K47" s="48" t="n">
         <f aca="false">K46*ns_gm</f>
-        <v>193229.164340488</v>
+        <v>289843.746510732</v>
       </c>
       <c r="L47" s="48" t="n">
         <f aca="false">L46*ns_gm</f>
-        <v>199174.677089426</v>
+        <v>298762.015634139</v>
       </c>
       <c r="M47" s="48" t="n">
         <f aca="false">M46*ns_gm</f>
-        <v>205120.189838364</v>
+        <v>307680.284757546</v>
       </c>
       <c r="N47" s="48" t="n">
         <f aca="false">N46*ns_gm</f>
-        <v>211065.702587302</v>
+        <v>316598.553880954</v>
       </c>
       <c r="O47" s="48" t="n">
         <f aca="false">O46*ns_gm</f>
-        <v>217011.215336241</v>
+        <v>325516.823004361</v>
       </c>
       <c r="P47" s="48" t="n">
         <f aca="false">P46*ns_gm</f>
-        <v>222956.728085179</v>
+        <v>334435.092127768</v>
       </c>
       <c r="Q47" s="48" t="n">
         <f aca="false">Q46*ns_gm</f>
-        <v>228902.240834117</v>
+        <v>343353.361251175</v>
       </c>
       <c r="R47" s="48" t="n">
         <f aca="false">R46*ns_gm</f>
-        <v>234847.753583055</v>
+        <v>352271.630374582</v>
       </c>
       <c r="S47" s="48" t="n">
         <f aca="false">S46*ns_gm</f>
-        <v>240793.266331993</v>
+        <v>361189.899497989</v>
       </c>
       <c r="T47" s="48" t="n">
         <f aca="false">T46*ns_gm</f>
-        <v>246738.779080931</v>
+        <v>370108.168621397</v>
       </c>
       <c r="U47" s="48" t="n">
         <f aca="false">U46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="V47" s="48" t="n">
         <f aca="false">V46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="W47" s="48" t="n">
         <f aca="false">W46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="X47" s="48" t="n">
         <f aca="false">X46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="Y47" s="48" t="n">
         <f aca="false">Y46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="Z47" s="48" t="n">
         <f aca="false">Z46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AA47" s="48" t="n">
         <f aca="false">AA46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AB47" s="48" t="n">
         <f aca="false">AB46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AC47" s="48" t="n">
         <f aca="false">AC46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AD47" s="48" t="n">
         <f aca="false">AD46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AE47" s="48" t="n">
         <f aca="false">AE46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AF47" s="48" t="n">
         <f aca="false">AF46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AG47" s="48" t="n">
         <f aca="false">AG46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AH47" s="48" t="n">
         <f aca="false">AH46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AI47" s="48" t="n">
         <f aca="false">AI46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AJ47" s="48" t="n">
         <f aca="false">AJ46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AK47" s="48" t="n">
         <f aca="false">AK46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AL47" s="48" t="n">
         <f aca="false">AL46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AM47" s="48" t="n">
         <f aca="false">AM46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AN47" s="48" t="n">
         <f aca="false">AN46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AO47" s="48" t="n">
         <f aca="false">AO46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AP47" s="48" t="n">
         <f aca="false">AP46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AQ47" s="48" t="n">
         <f aca="false">AQ46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AR47" s="48" t="n">
         <f aca="false">AR46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AS47" s="48" t="n">
         <f aca="false">AS46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AT47" s="48" t="n">
         <f aca="false">AT46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AU47" s="48" t="n">
         <f aca="false">AU46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AV47" s="48" t="n">
         <f aca="false">AV46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AW47" s="48" t="n">
         <f aca="false">AW46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AX47" s="48" t="n">
         <f aca="false">AX46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AY47" s="48" t="n">
         <f aca="false">AY46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="AZ47" s="48" t="n">
         <f aca="false">AZ46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="BA47" s="48" t="n">
         <f aca="false">BA46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="BB47" s="48" t="n">
         <f aca="false">BB46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="BC47" s="48" t="n">
         <f aca="false">BC46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="BD47" s="48" t="n">
         <f aca="false">BD46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="BE47" s="48" t="n">
         <f aca="false">BE46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="BF47" s="48" t="n">
         <f aca="false">BF46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="BG47" s="48" t="n">
         <f aca="false">BG46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="BH47" s="48" t="n">
         <f aca="false">BH46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="BI47" s="48" t="n">
         <f aca="false">BI46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="BJ47" s="48" t="n">
         <f aca="false">BJ46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
       <c r="BK47" s="48" t="n">
         <f aca="false">BK46*ns_gm</f>
-        <v>252684.291829869</v>
+        <v>379026.437744804</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D48" s="48" t="n">
         <f aca="false">D46*waste_actual</f>
-        <v>5946.39660022188</v>
+        <v>8919.59490033283</v>
       </c>
       <c r="E48" s="48" t="n">
         <f aca="false">E46*waste_actual</f>
-        <v>6179.58862376</v>
+        <v>9269.38293564</v>
       </c>
       <c r="F48" s="48" t="n">
         <f aca="false">F46*waste_actual</f>
-        <v>6412.78064729811</v>
+        <v>9619.17097094716</v>
       </c>
       <c r="G48" s="48" t="n">
         <f aca="false">G46*waste_actual</f>
-        <v>6645.97267083622</v>
+        <v>9968.95900625433</v>
       </c>
       <c r="H48" s="48" t="n">
         <f aca="false">H46*waste_actual</f>
-        <v>6879.16469437434</v>
+        <v>10318.7470415615</v>
       </c>
       <c r="I48" s="48" t="n">
         <f aca="false">I46*waste_actual</f>
-        <v>7112.35671791245</v>
+        <v>10668.5350768687</v>
       </c>
       <c r="J48" s="48" t="n">
         <f aca="false">J46*waste_actual</f>
-        <v>7345.54874145056</v>
+        <v>11018.3231121758</v>
       </c>
       <c r="K48" s="48" t="n">
         <f aca="false">K46*waste_actual</f>
-        <v>7578.74076498867</v>
+        <v>11368.111147483</v>
       </c>
       <c r="L48" s="48" t="n">
         <f aca="false">L46*waste_actual</f>
-        <v>7811.93278852679</v>
+        <v>11717.8991827902</v>
       </c>
       <c r="M48" s="48" t="n">
         <f aca="false">M46*waste_actual</f>
-        <v>8045.1248120649</v>
+        <v>12067.6872180974</v>
       </c>
       <c r="N48" s="48" t="n">
         <f aca="false">N46*waste_actual</f>
-        <v>8278.31683560301</v>
+        <v>12417.4752534045</v>
       </c>
       <c r="O48" s="48" t="n">
         <f aca="false">O46*waste_actual</f>
-        <v>8511.50885914113</v>
+        <v>12767.2632887117</v>
       </c>
       <c r="P48" s="48" t="n">
         <f aca="false">P46*waste_actual</f>
-        <v>8744.70088267924</v>
+        <v>13117.0513240189</v>
       </c>
       <c r="Q48" s="48" t="n">
         <f aca="false">Q46*waste_actual</f>
-        <v>8977.89290621735</v>
+        <v>13466.839359326</v>
       </c>
       <c r="R48" s="48" t="n">
         <f aca="false">R46*waste_actual</f>
-        <v>9211.08492975547</v>
+        <v>13816.6273946332</v>
       </c>
       <c r="S48" s="48" t="n">
         <f aca="false">S46*waste_actual</f>
-        <v>9444.27695329358</v>
+        <v>14166.4154299404</v>
       </c>
       <c r="T48" s="48" t="n">
         <f aca="false">T46*waste_actual</f>
-        <v>9677.46897683169</v>
+        <v>14516.2034652475</v>
       </c>
       <c r="U48" s="48" t="n">
         <f aca="false">U46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="V48" s="48" t="n">
         <f aca="false">V46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="W48" s="48" t="n">
         <f aca="false">W46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="X48" s="48" t="n">
         <f aca="false">X46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="Y48" s="48" t="n">
         <f aca="false">Y46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="Z48" s="48" t="n">
         <f aca="false">Z46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AA48" s="48" t="n">
         <f aca="false">AA46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AB48" s="48" t="n">
         <f aca="false">AB46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AC48" s="48" t="n">
         <f aca="false">AC46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AD48" s="48" t="n">
         <f aca="false">AD46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AE48" s="48" t="n">
         <f aca="false">AE46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AF48" s="48" t="n">
         <f aca="false">AF46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AG48" s="48" t="n">
         <f aca="false">AG46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AH48" s="48" t="n">
         <f aca="false">AH46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AI48" s="48" t="n">
         <f aca="false">AI46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AJ48" s="48" t="n">
         <f aca="false">AJ46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AK48" s="48" t="n">
         <f aca="false">AK46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AL48" s="48" t="n">
         <f aca="false">AL46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AM48" s="48" t="n">
         <f aca="false">AM46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AN48" s="48" t="n">
         <f aca="false">AN46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AO48" s="48" t="n">
         <f aca="false">AO46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AP48" s="48" t="n">
         <f aca="false">AP46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AQ48" s="48" t="n">
         <f aca="false">AQ46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AR48" s="48" t="n">
         <f aca="false">AR46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AS48" s="48" t="n">
         <f aca="false">AS46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AT48" s="48" t="n">
         <f aca="false">AT46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AU48" s="48" t="n">
         <f aca="false">AU46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AV48" s="48" t="n">
         <f aca="false">AV46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AW48" s="48" t="n">
         <f aca="false">AW46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AX48" s="48" t="n">
         <f aca="false">AX46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AY48" s="48" t="n">
         <f aca="false">AY46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="AZ48" s="48" t="n">
         <f aca="false">AZ46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="BA48" s="48" t="n">
         <f aca="false">BA46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="BB48" s="48" t="n">
         <f aca="false">BB46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="BC48" s="48" t="n">
         <f aca="false">BC46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="BD48" s="48" t="n">
         <f aca="false">BD46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="BE48" s="48" t="n">
         <f aca="false">BE46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="BF48" s="48" t="n">
         <f aca="false">BF46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="BG48" s="48" t="n">
         <f aca="false">BG46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="BH48" s="48" t="n">
         <f aca="false">BH46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="BI48" s="48" t="n">
         <f aca="false">BI46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="BJ48" s="48" t="n">
         <f aca="false">BJ46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
       <c r="BK48" s="48" t="n">
         <f aca="false">BK46*waste_actual</f>
-        <v>9910.66100036981</v>
+        <v>14865.9915005547</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D49" s="48" t="n">
         <f aca="false">MAX(D46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>85207.2139759259</v>
+        <v>127810.820963889</v>
       </c>
       <c r="E49" s="48" t="n">
         <f aca="false">MAX(E46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>85207.2139759259</v>
+        <v>127810.820963889</v>
       </c>
       <c r="F49" s="48" t="n">
         <f aca="false">MAX(F46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>85207.2139759259</v>
+        <v>127810.820963889</v>
       </c>
       <c r="G49" s="48" t="n">
         <f aca="false">MAX(G46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>85207.2139759259</v>
+        <v>127810.820963889</v>
       </c>
       <c r="H49" s="48" t="n">
         <f aca="false">MAX(H46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>85207.2139759259</v>
+        <v>127810.820963889</v>
       </c>
       <c r="I49" s="48" t="n">
         <f aca="false">MAX(I46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>85207.2139759259</v>
+        <v>127810.820963889</v>
       </c>
       <c r="J49" s="48" t="n">
         <f aca="false">MAX(J46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>85207.2139759259</v>
+        <v>127810.820963889</v>
       </c>
       <c r="K49" s="48" t="n">
         <f aca="false">MAX(K46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>85207.2139759259</v>
+        <v>127810.820963889</v>
       </c>
       <c r="L49" s="48" t="n">
         <f aca="false">MAX(L46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>85207.2139759259</v>
+        <v>127810.820963889</v>
       </c>
       <c r="M49" s="48" t="n">
         <f aca="false">MAX(M46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>85207.2139759259</v>
+        <v>127810.820963889</v>
       </c>
       <c r="N49" s="48" t="n">
         <f aca="false">MAX(N46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>85207.2139759259</v>
+        <v>127810.820963889</v>
       </c>
       <c r="O49" s="48" t="n">
         <f aca="false">MAX(O46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>86091.7179272331</v>
+        <v>129137.57689085</v>
       </c>
       <c r="P49" s="48" t="n">
         <f aca="false">MAX(P46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>88450.3951307189</v>
+        <v>132675.592696078</v>
       </c>
       <c r="Q49" s="48" t="n">
         <f aca="false">MAX(Q46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>90809.0723342048</v>
+        <v>136213.608501307</v>
       </c>
       <c r="R49" s="48" t="n">
         <f aca="false">MAX(R46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>93167.7495376906</v>
+        <v>139751.624306536</v>
       </c>
       <c r="S49" s="48" t="n">
         <f aca="false">MAX(S46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>95526.4267411764</v>
+        <v>143289.640111765</v>
       </c>
       <c r="T49" s="48" t="n">
         <f aca="false">MAX(T46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>97885.1039446623</v>
+        <v>146827.655916993</v>
       </c>
       <c r="U49" s="48" t="n">
         <f aca="false">MAX(U46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="V49" s="48" t="n">
         <f aca="false">MAX(V46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="W49" s="48" t="n">
         <f aca="false">MAX(W46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="X49" s="48" t="n">
         <f aca="false">MAX(X46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="Y49" s="48" t="n">
         <f aca="false">MAX(Y46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="Z49" s="48" t="n">
         <f aca="false">MAX(Z46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AA49" s="48" t="n">
         <f aca="false">MAX(AA46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AB49" s="48" t="n">
         <f aca="false">MAX(AB46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AC49" s="48" t="n">
         <f aca="false">MAX(AC46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AD49" s="48" t="n">
         <f aca="false">MAX(AD46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AE49" s="48" t="n">
         <f aca="false">MAX(AE46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AF49" s="48" t="n">
         <f aca="false">MAX(AF46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AG49" s="48" t="n">
         <f aca="false">MAX(AG46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AH49" s="48" t="n">
         <f aca="false">MAX(AH46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AI49" s="48" t="n">
         <f aca="false">MAX(AI46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AJ49" s="48" t="n">
         <f aca="false">MAX(AJ46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AK49" s="48" t="n">
         <f aca="false">MAX(AK46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AL49" s="48" t="n">
         <f aca="false">MAX(AL46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AM49" s="48" t="n">
         <f aca="false">MAX(AM46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AN49" s="48" t="n">
         <f aca="false">MAX(AN46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AO49" s="48" t="n">
         <f aca="false">MAX(AO46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AP49" s="48" t="n">
         <f aca="false">MAX(AP46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AQ49" s="48" t="n">
         <f aca="false">MAX(AQ46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AR49" s="48" t="n">
         <f aca="false">MAX(AR46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AS49" s="48" t="n">
         <f aca="false">MAX(AS46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AT49" s="48" t="n">
         <f aca="false">MAX(AT46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AU49" s="48" t="n">
         <f aca="false">MAX(AU46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AV49" s="48" t="n">
         <f aca="false">MAX(AV46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AW49" s="48" t="n">
         <f aca="false">MAX(AW46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AX49" s="48" t="n">
         <f aca="false">MAX(AX46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AY49" s="48" t="n">
         <f aca="false">MAX(AY46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="AZ49" s="48" t="n">
         <f aca="false">MAX(AZ46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="BA49" s="48" t="n">
         <f aca="false">MAX(BA46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="BB49" s="48" t="n">
         <f aca="false">MAX(BB46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="BC49" s="48" t="n">
         <f aca="false">MAX(BC46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="BD49" s="48" t="n">
         <f aca="false">MAX(BD46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="BE49" s="48" t="n">
         <f aca="false">MAX(BE46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="BF49" s="48" t="n">
         <f aca="false">MAX(BF46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="BG49" s="48" t="n">
         <f aca="false">MAX(BG46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="BH49" s="48" t="n">
         <f aca="false">MAX(BH46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="BI49" s="48" t="n">
         <f aca="false">MAX(BI46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="BJ49" s="48" t="n">
         <f aca="false">MAX(BJ46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
       <c r="BK49" s="48" t="n">
         <f aca="false">MAX(BK46*labor_pct,ns_mature_sales/12*labor_pct*labor_floor)</f>
-        <v>100243.781148148</v>
+        <v>150365.671722222</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6923,243 +6932,243 @@
       </c>
       <c r="D50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="E50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="F50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="G50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="H50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="I50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="J50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="K50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="L50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="M50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="N50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="O50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="P50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="Q50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="R50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="S50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="T50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="U50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="V50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="W50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="X50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="Y50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="Z50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AA50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AB50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AC50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AD50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AE50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AF50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AG50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AH50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AI50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AJ50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AK50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AL50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AM50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AN50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AO50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AP50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AQ50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AR50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AS50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AT50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AU50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AV50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AW50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AX50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AY50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="AZ50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="BA50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="BB50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="BC50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="BD50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="BE50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="BF50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="BG50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="BH50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="BI50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="BJ50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
       <c r="BK50" s="48" t="n">
         <f aca="false">sqft_new*rent_psf/12</f>
-        <v>40000</v>
+        <v>35250</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7168,1002 +7177,1002 @@
       </c>
       <c r="D51" s="48" t="n">
         <f aca="false">D46*other_pct</f>
-        <v>25324.7447111111</v>
+        <v>37987.1170666667</v>
       </c>
       <c r="E51" s="48" t="n">
         <f aca="false">E46*other_pct</f>
-        <v>26317.8719546841</v>
+        <v>39476.8079320261</v>
       </c>
       <c r="F51" s="48" t="n">
         <f aca="false">F46*other_pct</f>
-        <v>27310.9991982571</v>
+        <v>40966.4987973856</v>
       </c>
       <c r="G51" s="48" t="n">
         <f aca="false">G46*other_pct</f>
-        <v>28304.1264418301</v>
+        <v>42456.1896627451</v>
       </c>
       <c r="H51" s="48" t="n">
         <f aca="false">H46*other_pct</f>
-        <v>29297.253685403</v>
+        <v>43945.8805281046</v>
       </c>
       <c r="I51" s="48" t="n">
         <f aca="false">I46*other_pct</f>
-        <v>30290.380928976</v>
+        <v>45435.5713934641</v>
       </c>
       <c r="J51" s="48" t="n">
         <f aca="false">J46*other_pct</f>
-        <v>31283.508172549</v>
+        <v>46925.2622588235</v>
       </c>
       <c r="K51" s="48" t="n">
         <f aca="false">K46*other_pct</f>
-        <v>32276.635416122</v>
+        <v>48414.953124183</v>
       </c>
       <c r="L51" s="48" t="n">
         <f aca="false">L46*other_pct</f>
-        <v>33269.762659695</v>
+        <v>49904.6439895425</v>
       </c>
       <c r="M51" s="48" t="n">
         <f aca="false">M46*other_pct</f>
-        <v>34262.889903268</v>
+        <v>51394.334854902</v>
       </c>
       <c r="N51" s="48" t="n">
         <f aca="false">N46*other_pct</f>
-        <v>35256.0171468409</v>
+        <v>52884.0257202614</v>
       </c>
       <c r="O51" s="48" t="n">
         <f aca="false">O46*other_pct</f>
-        <v>36249.1443904139</v>
+        <v>54373.7165856209</v>
       </c>
       <c r="P51" s="48" t="n">
         <f aca="false">P46*other_pct</f>
-        <v>37242.2716339869</v>
+        <v>55863.4074509804</v>
       </c>
       <c r="Q51" s="48" t="n">
         <f aca="false">Q46*other_pct</f>
-        <v>38235.3988775599</v>
+        <v>57353.0983163399</v>
       </c>
       <c r="R51" s="48" t="n">
         <f aca="false">R46*other_pct</f>
-        <v>39228.5261211329</v>
+        <v>58842.7891816993</v>
       </c>
       <c r="S51" s="48" t="n">
         <f aca="false">S46*other_pct</f>
-        <v>40221.6533647059</v>
+        <v>60332.4800470588</v>
       </c>
       <c r="T51" s="48" t="n">
         <f aca="false">T46*other_pct</f>
-        <v>41214.7806082789</v>
+        <v>61822.1709124183</v>
       </c>
       <c r="U51" s="48" t="n">
         <f aca="false">U46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="V51" s="48" t="n">
         <f aca="false">V46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="W51" s="48" t="n">
         <f aca="false">W46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="X51" s="48" t="n">
         <f aca="false">X46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="Y51" s="48" t="n">
         <f aca="false">Y46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="Z51" s="48" t="n">
         <f aca="false">Z46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AA51" s="48" t="n">
         <f aca="false">AA46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AB51" s="48" t="n">
         <f aca="false">AB46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AC51" s="48" t="n">
         <f aca="false">AC46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AD51" s="48" t="n">
         <f aca="false">AD46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AE51" s="48" t="n">
         <f aca="false">AE46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AF51" s="48" t="n">
         <f aca="false">AF46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AG51" s="48" t="n">
         <f aca="false">AG46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AH51" s="48" t="n">
         <f aca="false">AH46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AI51" s="48" t="n">
         <f aca="false">AI46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AJ51" s="48" t="n">
         <f aca="false">AJ46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AK51" s="48" t="n">
         <f aca="false">AK46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AL51" s="48" t="n">
         <f aca="false">AL46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AM51" s="48" t="n">
         <f aca="false">AM46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AN51" s="48" t="n">
         <f aca="false">AN46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AO51" s="48" t="n">
         <f aca="false">AO46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AP51" s="48" t="n">
         <f aca="false">AP46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AQ51" s="48" t="n">
         <f aca="false">AQ46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AR51" s="48" t="n">
         <f aca="false">AR46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AS51" s="48" t="n">
         <f aca="false">AS46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AT51" s="48" t="n">
         <f aca="false">AT46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AU51" s="48" t="n">
         <f aca="false">AU46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AV51" s="48" t="n">
         <f aca="false">AV46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AW51" s="48" t="n">
         <f aca="false">AW46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AX51" s="48" t="n">
         <f aca="false">AX46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AY51" s="48" t="n">
         <f aca="false">AY46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="AZ51" s="48" t="n">
         <f aca="false">AZ46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="BA51" s="48" t="n">
         <f aca="false">BA46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="BB51" s="48" t="n">
         <f aca="false">BB46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="BC51" s="48" t="n">
         <f aca="false">BC46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="BD51" s="48" t="n">
         <f aca="false">BD46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="BE51" s="48" t="n">
         <f aca="false">BE46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="BF51" s="48" t="n">
         <f aca="false">BF46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="BG51" s="48" t="n">
         <f aca="false">BG46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="BH51" s="48" t="n">
         <f aca="false">BH46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="BI51" s="48" t="n">
         <f aca="false">BI46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="BJ51" s="48" t="n">
         <f aca="false">BJ46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
       <c r="BK51" s="48" t="n">
         <f aca="false">BK46*other_pct</f>
-        <v>42207.9078518518</v>
+        <v>63311.8617777778</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="43" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B52" s="54"/>
       <c r="C52" s="54"/>
       <c r="D52" s="55" t="n">
         <f aca="false">D47-D48-D49-D50-D51</f>
-        <v>-4867.78018933749</v>
+        <v>17448.3297159938</v>
       </c>
       <c r="E52" s="55" t="n">
         <f aca="false">E47-E48-E49-E50-E51</f>
-        <v>-148.58670751048</v>
+        <v>24527.1199387344</v>
       </c>
       <c r="F52" s="55" t="n">
         <f aca="false">F47-F48-F49-F50-F51</f>
-        <v>4570.60677431648</v>
+        <v>31605.9101614748</v>
       </c>
       <c r="G52" s="55" t="n">
         <f aca="false">G47-G48-G49-G50-G51</f>
-        <v>9289.8002561435</v>
+        <v>38684.7003842153</v>
       </c>
       <c r="H52" s="55" t="n">
         <f aca="false">H47-H48-H49-H50-H51</f>
-        <v>14008.9937379705</v>
+        <v>45763.4906069559</v>
       </c>
       <c r="I52" s="55" t="n">
         <f aca="false">I47-I48-I49-I50-I51</f>
-        <v>18728.1872197975</v>
+        <v>52842.2808296963</v>
       </c>
       <c r="J52" s="55" t="n">
         <f aca="false">J47-J48-J49-J50-J51</f>
-        <v>23447.3807016245</v>
+        <v>59921.0710524368</v>
       </c>
       <c r="K52" s="55" t="n">
         <f aca="false">K47-K48-K49-K50-K51</f>
-        <v>28166.5741834515</v>
+        <v>66999.8612751773</v>
       </c>
       <c r="L52" s="55" t="n">
         <f aca="false">L47-L48-L49-L50-L51</f>
-        <v>32885.7676652785</v>
+        <v>74078.6514979178</v>
       </c>
       <c r="M52" s="55" t="n">
         <f aca="false">M47-M48-M49-M50-M51</f>
-        <v>37604.9611471055</v>
+        <v>81157.4417206583</v>
       </c>
       <c r="N52" s="55" t="n">
         <f aca="false">N47-N48-N49-N50-N51</f>
-        <v>42324.1546289325</v>
+        <v>88236.2319433988</v>
       </c>
       <c r="O52" s="55" t="n">
         <f aca="false">O47-O48-O49-O50-O51</f>
-        <v>46158.8441594524</v>
+        <v>93988.2662391785</v>
       </c>
       <c r="P52" s="55" t="n">
         <f aca="false">P47-P48-P49-P50-P51</f>
-        <v>48519.3604377935</v>
+        <v>97529.0406566903</v>
       </c>
       <c r="Q52" s="55" t="n">
         <f aca="false">Q47-Q48-Q49-Q50-Q51</f>
-        <v>50879.8767161347</v>
+        <v>101069.815074202</v>
       </c>
       <c r="R52" s="55" t="n">
         <f aca="false">R47-R48-R49-R50-R51</f>
-        <v>53240.3929944758</v>
+        <v>104610.589491714</v>
       </c>
       <c r="S52" s="55" t="n">
         <f aca="false">S47-S48-S49-S50-S51</f>
-        <v>55600.9092728169</v>
+        <v>108151.363909225</v>
       </c>
       <c r="T52" s="55" t="n">
         <f aca="false">T47-T48-T49-T50-T51</f>
-        <v>57961.4255511581</v>
+        <v>111692.138326737</v>
       </c>
       <c r="U52" s="55" t="n">
         <f aca="false">U47-U48-U49-U50-U51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="V52" s="55" t="n">
         <f aca="false">V47-V48-V49-V50-V51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="W52" s="55" t="n">
         <f aca="false">W47-W48-W49-W50-W51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="X52" s="55" t="n">
         <f aca="false">X47-X48-X49-X50-X51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="Y52" s="55" t="n">
         <f aca="false">Y47-Y48-Y49-Y50-Y51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="Z52" s="55" t="n">
         <f aca="false">Z47-Z48-Z49-Z50-Z51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AA52" s="55" t="n">
         <f aca="false">AA47-AA48-AA49-AA50-AA51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AB52" s="55" t="n">
         <f aca="false">AB47-AB48-AB49-AB50-AB51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AC52" s="55" t="n">
         <f aca="false">AC47-AC48-AC49-AC50-AC51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AD52" s="55" t="n">
         <f aca="false">AD47-AD48-AD49-AD50-AD51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AE52" s="55" t="n">
         <f aca="false">AE47-AE48-AE49-AE50-AE51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AF52" s="55" t="n">
         <f aca="false">AF47-AF48-AF49-AF50-AF51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AG52" s="55" t="n">
         <f aca="false">AG47-AG48-AG49-AG50-AG51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AH52" s="55" t="n">
         <f aca="false">AH47-AH48-AH49-AH50-AH51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AI52" s="55" t="n">
         <f aca="false">AI47-AI48-AI49-AI50-AI51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AJ52" s="55" t="n">
         <f aca="false">AJ47-AJ48-AJ49-AJ50-AJ51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AK52" s="55" t="n">
         <f aca="false">AK47-AK48-AK49-AK50-AK51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AL52" s="55" t="n">
         <f aca="false">AL47-AL48-AL49-AL50-AL51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AM52" s="55" t="n">
         <f aca="false">AM47-AM48-AM49-AM50-AM51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AN52" s="55" t="n">
         <f aca="false">AN47-AN48-AN49-AN50-AN51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AO52" s="55" t="n">
         <f aca="false">AO47-AO48-AO49-AO50-AO51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AP52" s="55" t="n">
         <f aca="false">AP47-AP48-AP49-AP50-AP51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AQ52" s="55" t="n">
         <f aca="false">AQ47-AQ48-AQ49-AQ50-AQ51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AR52" s="55" t="n">
         <f aca="false">AR47-AR48-AR49-AR50-AR51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AS52" s="55" t="n">
         <f aca="false">AS47-AS48-AS49-AS50-AS51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AT52" s="55" t="n">
         <f aca="false">AT47-AT48-AT49-AT50-AT51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AU52" s="55" t="n">
         <f aca="false">AU47-AU48-AU49-AU50-AU51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AV52" s="55" t="n">
         <f aca="false">AV47-AV48-AV49-AV50-AV51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AW52" s="55" t="n">
         <f aca="false">AW47-AW48-AW49-AW50-AW51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AX52" s="55" t="n">
         <f aca="false">AX47-AX48-AX49-AX50-AX51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AY52" s="55" t="n">
         <f aca="false">AY47-AY48-AY49-AY50-AY51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AZ52" s="55" t="n">
         <f aca="false">AZ47-AZ48-AZ49-AZ50-AZ51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="BA52" s="55" t="n">
         <f aca="false">BA47-BA48-BA49-BA50-BA51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="BB52" s="55" t="n">
         <f aca="false">BB47-BB48-BB49-BB50-BB51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="BC52" s="55" t="n">
         <f aca="false">BC47-BC48-BC49-BC50-BC51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="BD52" s="55" t="n">
         <f aca="false">BD47-BD48-BD49-BD50-BD51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="BE52" s="55" t="n">
         <f aca="false">BE47-BE48-BE49-BE50-BE51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="BF52" s="55" t="n">
         <f aca="false">BF47-BF48-BF49-BF50-BF51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="BG52" s="55" t="n">
         <f aca="false">BG47-BG48-BG49-BG50-BG51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="BH52" s="55" t="n">
         <f aca="false">BH47-BH48-BH49-BH50-BH51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="BI52" s="55" t="n">
         <f aca="false">BI47-BI48-BI49-BI50-BI51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="BJ52" s="55" t="n">
         <f aca="false">BJ47-BJ48-BJ49-BJ50-BJ51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="BK52" s="55" t="n">
         <f aca="false">BK47-BK48-BK49-BK50-BK51</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C53" s="48" t="n">
         <f aca="false">-ns_invest</f>
-        <v>-2350000</v>
+        <v>-1995000</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C54" s="48" t="n">
         <f aca="false">C52+C53</f>
-        <v>-2350000</v>
+        <v>-1995000</v>
       </c>
       <c r="D54" s="48" t="n">
         <f aca="false">D52+D53</f>
-        <v>-4867.78018933749</v>
+        <v>17448.3297159938</v>
       </c>
       <c r="E54" s="48" t="n">
         <f aca="false">E52+E53</f>
-        <v>-148.58670751048</v>
+        <v>24527.1199387344</v>
       </c>
       <c r="F54" s="48" t="n">
         <f aca="false">F52+F53</f>
-        <v>4570.60677431648</v>
+        <v>31605.9101614748</v>
       </c>
       <c r="G54" s="48" t="n">
         <f aca="false">G52+G53</f>
-        <v>9289.8002561435</v>
+        <v>38684.7003842153</v>
       </c>
       <c r="H54" s="48" t="n">
         <f aca="false">H52+H53</f>
-        <v>14008.9937379705</v>
+        <v>45763.4906069559</v>
       </c>
       <c r="I54" s="48" t="n">
         <f aca="false">I52+I53</f>
-        <v>18728.1872197975</v>
+        <v>52842.2808296963</v>
       </c>
       <c r="J54" s="48" t="n">
         <f aca="false">J52+J53</f>
-        <v>23447.3807016245</v>
+        <v>59921.0710524368</v>
       </c>
       <c r="K54" s="48" t="n">
         <f aca="false">K52+K53</f>
-        <v>28166.5741834515</v>
+        <v>66999.8612751773</v>
       </c>
       <c r="L54" s="48" t="n">
         <f aca="false">L52+L53</f>
-        <v>32885.7676652785</v>
+        <v>74078.6514979178</v>
       </c>
       <c r="M54" s="48" t="n">
         <f aca="false">M52+M53</f>
-        <v>37604.9611471055</v>
+        <v>81157.4417206583</v>
       </c>
       <c r="N54" s="48" t="n">
         <f aca="false">N52+N53</f>
-        <v>42324.1546289325</v>
+        <v>88236.2319433988</v>
       </c>
       <c r="O54" s="48" t="n">
         <f aca="false">O52+O53</f>
-        <v>46158.8441594524</v>
+        <v>93988.2662391785</v>
       </c>
       <c r="P54" s="48" t="n">
         <f aca="false">P52+P53</f>
-        <v>48519.3604377935</v>
+        <v>97529.0406566903</v>
       </c>
       <c r="Q54" s="48" t="n">
         <f aca="false">Q52+Q53</f>
-        <v>50879.8767161347</v>
+        <v>101069.815074202</v>
       </c>
       <c r="R54" s="48" t="n">
         <f aca="false">R52+R53</f>
-        <v>53240.3929944758</v>
+        <v>104610.589491714</v>
       </c>
       <c r="S54" s="48" t="n">
         <f aca="false">S52+S53</f>
-        <v>55600.9092728169</v>
+        <v>108151.363909225</v>
       </c>
       <c r="T54" s="48" t="n">
         <f aca="false">T52+T53</f>
-        <v>57961.4255511581</v>
+        <v>111692.138326737</v>
       </c>
       <c r="U54" s="48" t="n">
         <f aca="false">U52+U53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="V54" s="48" t="n">
         <f aca="false">V52+V53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="W54" s="48" t="n">
         <f aca="false">W52+W53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="X54" s="48" t="n">
         <f aca="false">X52+X53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="Y54" s="48" t="n">
         <f aca="false">Y52+Y53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="Z54" s="48" t="n">
         <f aca="false">Z52+Z53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AA54" s="48" t="n">
         <f aca="false">AA52+AA53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AB54" s="48" t="n">
         <f aca="false">AB52+AB53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AC54" s="48" t="n">
         <f aca="false">AC52+AC53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AD54" s="48" t="n">
         <f aca="false">AD52+AD53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AE54" s="48" t="n">
         <f aca="false">AE52+AE53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AF54" s="48" t="n">
         <f aca="false">AF52+AF53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AG54" s="48" t="n">
         <f aca="false">AG52+AG53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AH54" s="48" t="n">
         <f aca="false">AH52+AH53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AI54" s="48" t="n">
         <f aca="false">AI52+AI53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AJ54" s="48" t="n">
         <f aca="false">AJ52+AJ53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AK54" s="48" t="n">
         <f aca="false">AK52+AK53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AL54" s="48" t="n">
         <f aca="false">AL52+AL53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AM54" s="48" t="n">
         <f aca="false">AM52+AM53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AN54" s="48" t="n">
         <f aca="false">AN52+AN53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AO54" s="48" t="n">
         <f aca="false">AO52+AO53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AP54" s="48" t="n">
         <f aca="false">AP52+AP53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AQ54" s="48" t="n">
         <f aca="false">AQ52+AQ53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AR54" s="48" t="n">
         <f aca="false">AR52+AR53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AS54" s="48" t="n">
         <f aca="false">AS52+AS53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AT54" s="48" t="n">
         <f aca="false">AT52+AT53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AU54" s="48" t="n">
         <f aca="false">AU52+AU53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AV54" s="48" t="n">
         <f aca="false">AV52+AV53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AW54" s="48" t="n">
         <f aca="false">AW52+AW53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AX54" s="48" t="n">
         <f aca="false">AX52+AX53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AY54" s="48" t="n">
         <f aca="false">AY52+AY53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="AZ54" s="48" t="n">
         <f aca="false">AZ52+AZ53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="BA54" s="48" t="n">
         <f aca="false">BA52+BA53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="BB54" s="48" t="n">
         <f aca="false">BB52+BB53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="BC54" s="48" t="n">
         <f aca="false">BC52+BC53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="BD54" s="48" t="n">
         <f aca="false">BD52+BD53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="BE54" s="48" t="n">
         <f aca="false">BE52+BE53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="BF54" s="48" t="n">
         <f aca="false">BF52+BF53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="BG54" s="48" t="n">
         <f aca="false">BG52+BG53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="BH54" s="48" t="n">
         <f aca="false">BH52+BH53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="BI54" s="48" t="n">
         <f aca="false">BI52+BI53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="BJ54" s="48" t="n">
         <f aca="false">BJ52+BJ53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
       <c r="BK54" s="48" t="n">
         <f aca="false">BK52+BK53</f>
-        <v>60321.9418294993</v>
+        <v>115232.912744249</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C55" s="56" t="n">
         <f aca="false">C54</f>
-        <v>-2350000</v>
+        <v>-1995000</v>
       </c>
       <c r="D55" s="56" t="n">
         <f aca="false">C55+D54</f>
-        <v>-2354867.78018934</v>
+        <v>-1977551.67028401</v>
       </c>
       <c r="E55" s="56" t="n">
         <f aca="false">D55+E54</f>
-        <v>-2355016.36689685</v>
+        <v>-1953024.55034527</v>
       </c>
       <c r="F55" s="56" t="n">
         <f aca="false">E55+F54</f>
-        <v>-2350445.76012253</v>
+        <v>-1921418.6401838</v>
       </c>
       <c r="G55" s="56" t="n">
         <f aca="false">F55+G54</f>
-        <v>-2341155.95986639</v>
+        <v>-1882733.93979958</v>
       </c>
       <c r="H55" s="56" t="n">
         <f aca="false">G55+H54</f>
-        <v>-2327146.96612842</v>
+        <v>-1836970.44919263</v>
       </c>
       <c r="I55" s="56" t="n">
         <f aca="false">H55+I54</f>
-        <v>-2308418.77890862</v>
+        <v>-1784128.16836293</v>
       </c>
       <c r="J55" s="56" t="n">
         <f aca="false">I55+J54</f>
-        <v>-2284971.398207</v>
+        <v>-1724207.09731049</v>
       </c>
       <c r="K55" s="56" t="n">
         <f aca="false">J55+K54</f>
-        <v>-2256804.82402354</v>
+        <v>-1657207.23603532</v>
       </c>
       <c r="L55" s="56" t="n">
         <f aca="false">K55+L54</f>
-        <v>-2223919.05635827</v>
+        <v>-1583128.5845374</v>
       </c>
       <c r="M55" s="56" t="n">
         <f aca="false">L55+M54</f>
-        <v>-2186314.09521116</v>
+        <v>-1501971.14281674</v>
       </c>
       <c r="N55" s="56" t="n">
         <f aca="false">M55+N54</f>
-        <v>-2143989.94058223</v>
+        <v>-1413734.91087334</v>
       </c>
       <c r="O55" s="56" t="n">
         <f aca="false">N55+O54</f>
-        <v>-2097831.09642278</v>
+        <v>-1319746.64463416</v>
       </c>
       <c r="P55" s="56" t="n">
         <f aca="false">O55+P54</f>
-        <v>-2049311.73598498</v>
+        <v>-1222217.60397747</v>
       </c>
       <c r="Q55" s="56" t="n">
         <f aca="false">P55+Q54</f>
-        <v>-1998431.85926885</v>
+        <v>-1121147.78890327</v>
       </c>
       <c r="R55" s="56" t="n">
         <f aca="false">Q55+R54</f>
-        <v>-1945191.46627437</v>
+        <v>-1016537.19941156</v>
       </c>
       <c r="S55" s="56" t="n">
         <f aca="false">R55+S54</f>
-        <v>-1889590.55700155</v>
+        <v>-908385.835502331</v>
       </c>
       <c r="T55" s="56" t="n">
         <f aca="false">S55+T54</f>
-        <v>-1831629.1314504</v>
+        <v>-796693.697175594</v>
       </c>
       <c r="U55" s="56" t="n">
         <f aca="false">T55+U54</f>
-        <v>-1771307.1896209</v>
+        <v>-681460.784431345</v>
       </c>
       <c r="V55" s="56" t="n">
         <f aca="false">U55+V54</f>
-        <v>-1710985.2477914</v>
+        <v>-566227.871687096</v>
       </c>
       <c r="W55" s="56" t="n">
         <f aca="false">V55+W54</f>
-        <v>-1650663.3059619</v>
+        <v>-450994.958942847</v>
       </c>
       <c r="X55" s="56" t="n">
         <f aca="false">W55+X54</f>
-        <v>-1590341.3641324</v>
+        <v>-335762.046198598</v>
       </c>
       <c r="Y55" s="56" t="n">
         <f aca="false">X55+Y54</f>
-        <v>-1530019.4223029</v>
+        <v>-220529.133454349</v>
       </c>
       <c r="Z55" s="56" t="n">
         <f aca="false">Y55+Z54</f>
-        <v>-1469697.4804734</v>
+        <v>-105296.2207101</v>
       </c>
       <c r="AA55" s="56" t="n">
         <f aca="false">Z55+AA54</f>
-        <v>-1409375.5386439</v>
+        <v>9936.69203414887</v>
       </c>
       <c r="AB55" s="56" t="n">
         <f aca="false">AA55+AB54</f>
-        <v>-1349053.5968144</v>
+        <v>125169.604778398</v>
       </c>
       <c r="AC55" s="56" t="n">
         <f aca="false">AB55+AC54</f>
-        <v>-1288731.6549849</v>
+        <v>240402.517522647</v>
       </c>
       <c r="AD55" s="56" t="n">
         <f aca="false">AC55+AD54</f>
-        <v>-1228409.7131554</v>
+        <v>355635.430266896</v>
       </c>
       <c r="AE55" s="56" t="n">
         <f aca="false">AD55+AE54</f>
-        <v>-1168087.7713259</v>
+        <v>470868.343011145</v>
       </c>
       <c r="AF55" s="56" t="n">
         <f aca="false">AE55+AF54</f>
-        <v>-1107765.8294964</v>
+        <v>586101.255755394</v>
       </c>
       <c r="AG55" s="56" t="n">
         <f aca="false">AF55+AG54</f>
-        <v>-1047443.88766691</v>
+        <v>701334.168499643</v>
       </c>
       <c r="AH55" s="56" t="n">
         <f aca="false">AG55+AH54</f>
-        <v>-987121.945837406</v>
+        <v>816567.081243892</v>
       </c>
       <c r="AI55" s="56" t="n">
         <f aca="false">AH55+AI54</f>
-        <v>-926800.004007907</v>
+        <v>931799.993988141</v>
       </c>
       <c r="AJ55" s="56" t="n">
         <f aca="false">AI55+AJ54</f>
-        <v>-866478.062178408</v>
+        <v>1047032.90673239</v>
       </c>
       <c r="AK55" s="56" t="n">
         <f aca="false">AJ55+AK54</f>
-        <v>-806156.120348909</v>
+        <v>1162265.81947664</v>
       </c>
       <c r="AL55" s="56" t="n">
         <f aca="false">AK55+AL54</f>
-        <v>-745834.17851941</v>
+        <v>1277498.73222089</v>
       </c>
       <c r="AM55" s="56" t="n">
         <f aca="false">AL55+AM54</f>
-        <v>-685512.23668991</v>
+        <v>1392731.64496514</v>
       </c>
       <c r="AN55" s="56" t="n">
         <f aca="false">AM55+AN54</f>
-        <v>-625190.294860411</v>
+        <v>1507964.55770939</v>
       </c>
       <c r="AO55" s="56" t="n">
         <f aca="false">AN55+AO54</f>
-        <v>-564868.353030912</v>
+        <v>1623197.47045363</v>
       </c>
       <c r="AP55" s="56" t="n">
         <f aca="false">AO55+AP54</f>
-        <v>-504546.411201413</v>
+        <v>1738430.38319788</v>
       </c>
       <c r="AQ55" s="56" t="n">
         <f aca="false">AP55+AQ54</f>
-        <v>-444224.469371913</v>
+        <v>1853663.29594213</v>
       </c>
       <c r="AR55" s="56" t="n">
         <f aca="false">AQ55+AR54</f>
-        <v>-383902.527542414</v>
+        <v>1968896.20868638</v>
       </c>
       <c r="AS55" s="56" t="n">
         <f aca="false">AR55+AS54</f>
-        <v>-323580.585712915</v>
+        <v>2084129.12143063</v>
       </c>
       <c r="AT55" s="56" t="n">
         <f aca="false">AS55+AT54</f>
-        <v>-263258.643883416</v>
+        <v>2199362.03417488</v>
       </c>
       <c r="AU55" s="56" t="n">
         <f aca="false">AT55+AU54</f>
-        <v>-202936.702053916</v>
+        <v>2314594.94691913</v>
       </c>
       <c r="AV55" s="56" t="n">
         <f aca="false">AU55+AV54</f>
-        <v>-142614.760224417</v>
+        <v>2429827.85966338</v>
       </c>
       <c r="AW55" s="56" t="n">
         <f aca="false">AV55+AW54</f>
-        <v>-82292.8183949179</v>
+        <v>2545060.77240763</v>
       </c>
       <c r="AX55" s="56" t="n">
         <f aca="false">AW55+AX54</f>
-        <v>-21970.8765654186</v>
+        <v>2660293.68515187</v>
       </c>
       <c r="AY55" s="56" t="n">
         <f aca="false">AX55+AY54</f>
-        <v>38351.0652640806</v>
+        <v>2775526.59789612</v>
       </c>
       <c r="AZ55" s="56" t="n">
         <f aca="false">AY55+AZ54</f>
-        <v>98673.0070935799</v>
+        <v>2890759.51064037</v>
       </c>
       <c r="BA55" s="56" t="n">
         <f aca="false">AZ55+BA54</f>
-        <v>158994.948923079</v>
+        <v>3005992.42338462</v>
       </c>
       <c r="BB55" s="56" t="n">
         <f aca="false">BA55+BB54</f>
-        <v>219316.890752578</v>
+        <v>3121225.33612887</v>
       </c>
       <c r="BC55" s="56" t="n">
         <f aca="false">BB55+BC54</f>
-        <v>279638.832582078</v>
+        <v>3236458.24887312</v>
       </c>
       <c r="BD55" s="56" t="n">
         <f aca="false">BC55+BD54</f>
-        <v>339960.774411577</v>
+        <v>3351691.16161737</v>
       </c>
       <c r="BE55" s="56" t="n">
         <f aca="false">BD55+BE54</f>
-        <v>400282.716241076</v>
+        <v>3466924.07436162</v>
       </c>
       <c r="BF55" s="56" t="n">
         <f aca="false">BE55+BF54</f>
-        <v>460604.658070575</v>
+        <v>3582156.98710586</v>
       </c>
       <c r="BG55" s="56" t="n">
         <f aca="false">BF55+BG54</f>
-        <v>520926.599900075</v>
+        <v>3697389.89985011</v>
       </c>
       <c r="BH55" s="56" t="n">
         <f aca="false">BG55+BH54</f>
-        <v>581248.541729574</v>
+        <v>3812622.81259436</v>
       </c>
       <c r="BI55" s="56" t="n">
         <f aca="false">BH55+BI54</f>
-        <v>641570.483559073</v>
+        <v>3927855.72533861</v>
       </c>
       <c r="BJ55" s="56" t="n">
         <f aca="false">BI55+BJ54</f>
-        <v>701892.425388572</v>
+        <v>4043088.63808286</v>
       </c>
       <c r="BK55" s="56" t="n">
         <f aca="false">BJ55+BK54</f>
-        <v>762214.367218072</v>
+        <v>4158321.55082711</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D56" s="57" t="n">
         <f aca="false">IF(D55&gt;=0,D$43,999)</f>
@@ -8259,99 +8268,99 @@
       </c>
       <c r="AA56" s="58" t="n">
         <f aca="false">IF(AA55&gt;=0,AA$43,999)</f>
-        <v>999</v>
+        <v>24</v>
       </c>
       <c r="AB56" s="58" t="n">
         <f aca="false">IF(AB55&gt;=0,AB$43,999)</f>
-        <v>999</v>
+        <v>25</v>
       </c>
       <c r="AC56" s="58" t="n">
         <f aca="false">IF(AC55&gt;=0,AC$43,999)</f>
-        <v>999</v>
+        <v>26</v>
       </c>
       <c r="AD56" s="58" t="n">
         <f aca="false">IF(AD55&gt;=0,AD$43,999)</f>
-        <v>999</v>
+        <v>27</v>
       </c>
       <c r="AE56" s="58" t="n">
         <f aca="false">IF(AE55&gt;=0,AE$43,999)</f>
-        <v>999</v>
+        <v>28</v>
       </c>
       <c r="AF56" s="58" t="n">
         <f aca="false">IF(AF55&gt;=0,AF$43,999)</f>
-        <v>999</v>
+        <v>29</v>
       </c>
       <c r="AG56" s="58" t="n">
         <f aca="false">IF(AG55&gt;=0,AG$43,999)</f>
-        <v>999</v>
+        <v>30</v>
       </c>
       <c r="AH56" s="58" t="n">
         <f aca="false">IF(AH55&gt;=0,AH$43,999)</f>
-        <v>999</v>
+        <v>31</v>
       </c>
       <c r="AI56" s="58" t="n">
         <f aca="false">IF(AI55&gt;=0,AI$43,999)</f>
-        <v>999</v>
+        <v>32</v>
       </c>
       <c r="AJ56" s="58" t="n">
         <f aca="false">IF(AJ55&gt;=0,AJ$43,999)</f>
-        <v>999</v>
+        <v>33</v>
       </c>
       <c r="AK56" s="58" t="n">
         <f aca="false">IF(AK55&gt;=0,AK$43,999)</f>
-        <v>999</v>
+        <v>34</v>
       </c>
       <c r="AL56" s="58" t="n">
         <f aca="false">IF(AL55&gt;=0,AL$43,999)</f>
-        <v>999</v>
+        <v>35</v>
       </c>
       <c r="AM56" s="58" t="n">
         <f aca="false">IF(AM55&gt;=0,AM$43,999)</f>
-        <v>999</v>
+        <v>36</v>
       </c>
       <c r="AN56" s="58" t="n">
         <f aca="false">IF(AN55&gt;=0,AN$43,999)</f>
-        <v>999</v>
+        <v>37</v>
       </c>
       <c r="AO56" s="58" t="n">
         <f aca="false">IF(AO55&gt;=0,AO$43,999)</f>
-        <v>999</v>
+        <v>38</v>
       </c>
       <c r="AP56" s="58" t="n">
         <f aca="false">IF(AP55&gt;=0,AP$43,999)</f>
-        <v>999</v>
+        <v>39</v>
       </c>
       <c r="AQ56" s="58" t="n">
         <f aca="false">IF(AQ55&gt;=0,AQ$43,999)</f>
-        <v>999</v>
+        <v>40</v>
       </c>
       <c r="AR56" s="58" t="n">
         <f aca="false">IF(AR55&gt;=0,AR$43,999)</f>
-        <v>999</v>
+        <v>41</v>
       </c>
       <c r="AS56" s="58" t="n">
         <f aca="false">IF(AS55&gt;=0,AS$43,999)</f>
-        <v>999</v>
+        <v>42</v>
       </c>
       <c r="AT56" s="58" t="n">
         <f aca="false">IF(AT55&gt;=0,AT$43,999)</f>
-        <v>999</v>
+        <v>43</v>
       </c>
       <c r="AU56" s="58" t="n">
         <f aca="false">IF(AU55&gt;=0,AU$43,999)</f>
-        <v>999</v>
+        <v>44</v>
       </c>
       <c r="AV56" s="58" t="n">
         <f aca="false">IF(AV55&gt;=0,AV$43,999)</f>
-        <v>999</v>
+        <v>45</v>
       </c>
       <c r="AW56" s="58" t="n">
         <f aca="false">IF(AW55&gt;=0,AW$43,999)</f>
-        <v>999</v>
+        <v>46</v>
       </c>
       <c r="AX56" s="58" t="n">
         <f aca="false">IF(AX55&gt;=0,AX$43,999)</f>
-        <v>999</v>
+        <v>47</v>
       </c>
       <c r="AY56" s="58" t="n">
         <f aca="false">IF(AY55&gt;=0,AY$43,999)</f>
@@ -8433,7 +8442,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8444,7 +8453,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -8454,7 +8463,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B5" s="59" t="n">
         <f aca="false">cash_open</f>
@@ -8463,11 +8472,11 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B6" s="24" t="n">
         <f aca="false">MIN(H28:T28)</f>
-        <v>-1134848.27174883</v>
+        <v>-651098.271748835</v>
       </c>
       <c r="C6" s="5" t="str">
         <f aca="false">"in week "&amp;INDEX(H12:T12,MATCH(B6,H28:T28,0))</f>
@@ -8476,34 +8485,34 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B7" s="24" t="n">
         <f aca="false">T28</f>
-        <v>-1134848.27174883</v>
+        <v>-651098.271748835</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B8" s="24" t="n">
         <f aca="false">MAX(0,cash_cushion-B6)</f>
-        <v>1384848.27174883</v>
+        <v>901098.271748835</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B9" s="24" t="n">
         <f aca="false">SUM(H25:T25)</f>
-        <v>230151.728251165</v>
+        <v>394401.728251165</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -8527,7 +8536,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B12" s="60" t="n">
         <v>-6</v>
@@ -8589,7 +8598,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B13" s="61" t="n">
         <f aca="false">C13-7</f>
@@ -8669,7 +8678,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B14" s="63" t="n">
         <f aca="false">Data!D31</f>
@@ -8750,7 +8759,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B15" s="63" t="n">
         <f aca="false">Data!G31</f>
@@ -8831,12 +8840,12 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H18" s="48" t="n">
         <f aca="false">H14</f>
@@ -8893,12 +8902,12 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H20" s="48" t="n">
         <f aca="false">Data!$D$42*INDEX($B$15:$T$15,COLUMN()-1-Data!$E$42)+Data!$D$43*INDEX($B$15:$T$15,COLUMN()-1-Data!$E$43)+Data!$D$44*INDEX($B$15:$T$15,COLUMN()-1-Data!$E$44)+Data!$D$45*INDEX($B$15:$T$15,COLUMN()-1-Data!$E$45)+Data!$D$46*INDEX($B$15:$T$15,COLUMN()-1-Data!$E$46)</f>
@@ -8955,7 +8964,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H21" s="48" t="n">
         <f aca="false">IF(ISODD(H$12),labor_pct*(F14+G14),0)</f>
@@ -9012,11 +9021,11 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H22" s="48" t="n">
         <f aca="false">IF(DAY(H$13+6)&lt;=7,(sqft_s1+sqft_s2+sqft_s3)*rent_psf/12,0)</f>
-        <v>135000</v>
+        <v>80250</v>
       </c>
       <c r="I22" s="48" t="n">
         <f aca="false">IF(DAY(I$13+6)&lt;=7,(sqft_s1+sqft_s2+sqft_s3)*rent_psf/12,0)</f>
@@ -9032,7 +9041,7 @@
       </c>
       <c r="L22" s="48" t="n">
         <f aca="false">IF(DAY(L$13+6)&lt;=7,(sqft_s1+sqft_s2+sqft_s3)*rent_psf/12,0)</f>
-        <v>135000</v>
+        <v>80250</v>
       </c>
       <c r="M22" s="48" t="n">
         <f aca="false">IF(DAY(M$13+6)&lt;=7,(sqft_s1+sqft_s2+sqft_s3)*rent_psf/12,0)</f>
@@ -9052,7 +9061,7 @@
       </c>
       <c r="Q22" s="48" t="n">
         <f aca="false">IF(DAY(Q$13+6)&lt;=7,(sqft_s1+sqft_s2+sqft_s3)*rent_psf/12,0)</f>
-        <v>135000</v>
+        <v>80250</v>
       </c>
       <c r="R22" s="48" t="n">
         <f aca="false">IF(DAY(R$13+6)&lt;=7,(sqft_s1+sqft_s2+sqft_s3)*rent_psf/12,0)</f>
@@ -9126,7 +9135,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H24" s="48" t="n">
         <f aca="false">ho_pct*H14</f>
@@ -9183,7 +9192,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="43" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B25" s="54"/>
       <c r="C25" s="54"/>
@@ -9193,7 +9202,7 @@
       <c r="G25" s="54"/>
       <c r="H25" s="55" t="n">
         <f aca="false">H18-SUM(H20:H24)</f>
-        <v>-138446.807751655</v>
+        <v>-83696.8077516548</v>
       </c>
       <c r="I25" s="55" t="n">
         <f aca="false">I18-SUM(I20:I24)</f>
@@ -9209,7 +9218,7 @@
       </c>
       <c r="L25" s="55" t="n">
         <f aca="false">L18-SUM(L20:L24)</f>
-        <v>-154896.223367115</v>
+        <v>-100146.223367115</v>
       </c>
       <c r="M25" s="55" t="n">
         <f aca="false">M18-SUM(M20:M24)</f>
@@ -9229,7 +9238,7 @@
       </c>
       <c r="Q25" s="55" t="n">
         <f aca="false">Q18-SUM(Q20:Q24)</f>
-        <v>-13421.8094494661</v>
+        <v>41328.1905505339</v>
       </c>
       <c r="R25" s="55" t="n">
         <f aca="false">R18-SUM(R20:R24)</f>
@@ -9246,7 +9255,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H26" s="48" t="n">
         <f aca="false">IF(AND(build_start&gt;0,H$12&gt;=build_start,H$12&lt;build_start+build_weeks),ns_invest/build_weeks,0)</f>
@@ -9266,48 +9275,48 @@
       </c>
       <c r="L26" s="48" t="n">
         <f aca="false">IF(AND(build_start&gt;0,L$12&gt;=build_start,L$12&lt;build_start+build_weeks),ns_invest/build_weeks,0)</f>
-        <v>235000</v>
+        <v>199500</v>
       </c>
       <c r="M26" s="48" t="n">
         <f aca="false">IF(AND(build_start&gt;0,M$12&gt;=build_start,M$12&lt;build_start+build_weeks),ns_invest/build_weeks,0)</f>
-        <v>235000</v>
+        <v>199500</v>
       </c>
       <c r="N26" s="48" t="n">
         <f aca="false">IF(AND(build_start&gt;0,N$12&gt;=build_start,N$12&lt;build_start+build_weeks),ns_invest/build_weeks,0)</f>
-        <v>235000</v>
+        <v>199500</v>
       </c>
       <c r="O26" s="48" t="n">
         <f aca="false">IF(AND(build_start&gt;0,O$12&gt;=build_start,O$12&lt;build_start+build_weeks),ns_invest/build_weeks,0)</f>
-        <v>235000</v>
+        <v>199500</v>
       </c>
       <c r="P26" s="48" t="n">
         <f aca="false">IF(AND(build_start&gt;0,P$12&gt;=build_start,P$12&lt;build_start+build_weeks),ns_invest/build_weeks,0)</f>
-        <v>235000</v>
+        <v>199500</v>
       </c>
       <c r="Q26" s="48" t="n">
         <f aca="false">IF(AND(build_start&gt;0,Q$12&gt;=build_start,Q$12&lt;build_start+build_weeks),ns_invest/build_weeks,0)</f>
-        <v>235000</v>
+        <v>199500</v>
       </c>
       <c r="R26" s="48" t="n">
         <f aca="false">IF(AND(build_start&gt;0,R$12&gt;=build_start,R$12&lt;build_start+build_weeks),ns_invest/build_weeks,0)</f>
-        <v>235000</v>
+        <v>199500</v>
       </c>
       <c r="S26" s="48" t="n">
         <f aca="false">IF(AND(build_start&gt;0,S$12&gt;=build_start,S$12&lt;build_start+build_weeks),ns_invest/build_weeks,0)</f>
-        <v>235000</v>
+        <v>199500</v>
       </c>
       <c r="T26" s="48" t="n">
         <f aca="false">IF(AND(build_start&gt;0,T$12&gt;=build_start,T$12&lt;build_start+build_weeks),ns_invest/build_weeks,0)</f>
-        <v>235000</v>
+        <v>199500</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H27" s="48" t="n">
         <f aca="false">H25-H26</f>
-        <v>-138446.807751655</v>
+        <v>-83696.8077516548</v>
       </c>
       <c r="I27" s="48" t="n">
         <f aca="false">I25-I26</f>
@@ -9323,44 +9332,44 @@
       </c>
       <c r="L27" s="48" t="n">
         <f aca="false">L25-L26</f>
-        <v>-389896.223367115</v>
+        <v>-299646.223367115</v>
       </c>
       <c r="M27" s="48" t="n">
         <f aca="false">M25-M26</f>
-        <v>-114124.716211634</v>
+        <v>-78624.7162116339</v>
       </c>
       <c r="N27" s="48" t="n">
         <f aca="false">N25-N26</f>
-        <v>-253358.117522799</v>
+        <v>-217858.117522799</v>
       </c>
       <c r="O27" s="48" t="n">
         <f aca="false">O25-O26</f>
-        <v>-113421.809449466</v>
+        <v>-77921.8094494661</v>
       </c>
       <c r="P27" s="48" t="n">
         <f aca="false">P25-P26</f>
-        <v>-253358.117522799</v>
+        <v>-217858.117522799</v>
       </c>
       <c r="Q27" s="48" t="n">
         <f aca="false">Q25-Q26</f>
-        <v>-248421.809449466</v>
+        <v>-158171.809449466</v>
       </c>
       <c r="R27" s="48" t="n">
         <f aca="false">R25-R26</f>
-        <v>-253358.117522799</v>
+        <v>-217858.117522799</v>
       </c>
       <c r="S27" s="48" t="n">
         <f aca="false">S25-S26</f>
-        <v>-113421.809449466</v>
+        <v>-77921.8094494661</v>
       </c>
       <c r="T27" s="48" t="n">
         <f aca="false">T25-T26</f>
-        <v>-253358.117522799</v>
+        <v>-217858.117522799</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="43" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B28" s="54"/>
       <c r="C28" s="54"/>
@@ -9370,60 +9379,60 @@
       <c r="G28" s="54"/>
       <c r="H28" s="55" t="n">
         <f aca="false">cash_open+H27</f>
-        <v>611553.192248345</v>
+        <v>666303.192248345</v>
       </c>
       <c r="I28" s="55" t="n">
         <f aca="false">H28+I27</f>
-        <v>744963.804998198</v>
+        <v>799713.804998198</v>
       </c>
       <c r="J28" s="55" t="n">
         <f aca="false">I28+J27</f>
-        <v>734250.647872111</v>
+        <v>789000.647872111</v>
       </c>
       <c r="K28" s="55" t="n">
         <f aca="false">J28+K27</f>
-        <v>857870.56626951</v>
+        <v>912620.56626951</v>
       </c>
       <c r="L28" s="55" t="n">
         <f aca="false">K28+L27</f>
-        <v>467974.342902395</v>
+        <v>612974.342902395</v>
       </c>
       <c r="M28" s="55" t="n">
         <f aca="false">L28+M27</f>
-        <v>353849.626690761</v>
+        <v>534349.626690761</v>
       </c>
       <c r="N28" s="55" t="n">
         <f aca="false">M28+N27</f>
-        <v>100491.509167962</v>
+        <v>316491.509167962</v>
       </c>
       <c r="O28" s="55" t="n">
         <f aca="false">N28+O27</f>
-        <v>-12930.3002815043</v>
+        <v>238569.699718496</v>
       </c>
       <c r="P28" s="55" t="n">
         <f aca="false">O28+P27</f>
-        <v>-266288.417804304</v>
+        <v>20711.5821956963</v>
       </c>
       <c r="Q28" s="55" t="n">
         <f aca="false">P28+Q27</f>
-        <v>-514710.22725377</v>
+        <v>-137460.22725377</v>
       </c>
       <c r="R28" s="55" t="n">
         <f aca="false">Q28+R27</f>
-        <v>-768068.344776569</v>
+        <v>-355318.344776569</v>
       </c>
       <c r="S28" s="55" t="n">
         <f aca="false">R28+S27</f>
-        <v>-881490.154226035</v>
+        <v>-433240.154226035</v>
       </c>
       <c r="T28" s="55" t="n">
         <f aca="false">S28+T27</f>
-        <v>-1134848.27174883</v>
+        <v>-651098.271748835</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H29" s="64" t="n">
         <f aca="false">cash_cushion</f>
@@ -9480,7 +9489,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H30" s="65" t="str">
         <f aca="false">IF(H28&lt;cash_cushion,"below","")</f>
@@ -9508,7 +9517,7 @@
       </c>
       <c r="N30" s="65" t="str">
         <f aca="false">IF(N28&lt;cash_cushion,"below","")</f>
-        <v>below</v>
+        <v/>
       </c>
       <c r="O30" s="65" t="str">
         <f aca="false">IF(O28&lt;cash_cushion,"below","")</f>
@@ -9537,7 +9546,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -9577,17 +9586,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -9602,7 +9611,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B5" s="24" t="n">
         <f aca="false">B19</f>
@@ -9611,7 +9620,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B6" s="66" t="n">
         <f aca="false">D19</f>
@@ -9620,7 +9629,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B7" s="24" t="n">
         <f aca="false">I19</f>
@@ -9629,7 +9638,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B8" s="19" t="n">
         <f aca="false">J19</f>
@@ -9638,7 +9647,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -9653,37 +9662,37 @@
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I10" s="17" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J10" s="17" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10056,7 +10065,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="43" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B19" s="44" t="n">
         <f aca="false">SUM(B11:B18)</f>
@@ -10092,7 +10101,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B21" s="3" t="str">
         <f aca="false">INDEX(A11:A18,MATCH(MAX(I11:I18),I11:I18,0))</f>
@@ -10101,7 +10110,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -10135,29 +10144,29 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B4" s="74" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C4" s="74"/>
       <c r="D4" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -10167,7 +10176,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B7" s="75" t="n">
         <f aca="false">INDEX(Data!$G$15:$G$23,MATCH(category,category_list,0))</f>
@@ -10176,7 +10185,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B8" s="75" t="n">
         <f aca="false">INDEX(Data!$H$15:$H$23,MATCH(category,category_list,0))</f>
@@ -10185,7 +10194,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B9" s="76" t="n">
         <f aca="false">INDEX(Data!$I$15:$I$23,MATCH(category,category_list,0))</f>
@@ -10194,7 +10203,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B10" s="77" t="n">
         <f aca="false">IF(B7=0,0,(B7-B8)/B7)</f>
@@ -10203,19 +10212,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B11" s="78" t="n">
         <f aca="false">INDEX(Data!$F$15:$F$23,MATCH(category,category_list,0))</f>
         <v>0.28</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B12" s="79" t="n">
         <f aca="false">B10-B11</f>
@@ -10224,7 +10233,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B13" s="80" t="n">
         <v>0.03</v>
@@ -10232,18 +10241,18 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B14" s="81" t="n">
         <v>-1.2</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B15" s="82" t="n">
         <f aca="false">B7*(1+B13)</f>
@@ -10252,7 +10261,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B16" s="83" t="n">
         <f aca="false">MAX(0,B9*(1+B14*B13))</f>
@@ -10261,7 +10270,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B17" s="84" t="n">
         <f aca="false">(B7-B8)*B9</f>
@@ -10270,7 +10279,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B18" s="84" t="n">
         <f aca="false">(B15-B8)*B16</f>
@@ -10279,7 +10288,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B19" s="40" t="n">
         <f aca="false">(B18-B17)*52</f>
@@ -10288,7 +10297,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B20" s="77" t="n">
         <f aca="false">IF(B15=0,0,(B15-B8)/B15)</f>
@@ -10297,19 +10306,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B21" s="79" t="n">
         <f aca="false">IF(B15-B8&lt;=0,"Below cost",(B7-B8)/(B15-B8)-1)</f>
         <v>-0.110777680993136</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10506,7 +10515,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -10516,7 +10525,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B34" s="87" t="n">
         <v>0.2</v>
@@ -10524,7 +10533,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B35" s="88" t="n">
         <v>2</v>
@@ -10532,18 +10541,18 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B36" s="87" t="n">
         <v>0.5</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B37" s="89" t="n">
         <v>0.5</v>
@@ -10551,7 +10560,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B38" s="82" t="n">
         <f aca="false">B7*(1-B34)</f>
@@ -10560,7 +10569,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B39" s="82" t="n">
         <f aca="false">B38-B8+B7*B34*B37</f>
@@ -10569,7 +10578,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B40" s="40" t="n">
         <f aca="false">(B39*B9*(1+B36)-(B7-B8)*B9)*B35</f>
@@ -10578,19 +10587,19 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B41" s="90" t="n">
         <f aca="false">IF(B39&lt;=0,"Sells below cost",(B7-B8)/B39-1)</f>
         <v>0.710163348360449</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B42" s="91" t="str">
         <f aca="false">IF(B34&gt;0.3,"Over the 30% cap: needs COO approval","Within the 30% cap")</f>
@@ -10632,17 +10641,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B3" s="23" t="n">
         <v>30</v>
@@ -10650,7 +10659,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -10668,48 +10677,48 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M6" s="17" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B7" s="23" t="n">
         <v>30</v>
@@ -10755,7 +10764,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B8" s="23" t="n">
         <v>30</v>
@@ -10801,7 +10810,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B9" s="23" t="n">
         <v>19</v>
@@ -10847,7 +10856,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="43" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B10" s="54"/>
       <c r="C10" s="44" t="n">
@@ -10897,12 +10906,12 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -10920,51 +10929,51 @@
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L14" s="17" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M14" s="17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B15" s="25" t="n">
         <v>127119.22</v>
@@ -11012,7 +11021,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B16" s="25" t="n">
         <v>164813.46</v>
@@ -11060,7 +11069,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B17" s="25" t="n">
         <v>71979.37</v>
@@ -11108,7 +11117,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B18" s="25" t="n">
         <v>141755.02</v>
@@ -11156,7 +11165,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B19" s="25" t="n">
         <v>67439.28</v>
@@ -11204,7 +11213,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B20" s="25" t="n">
         <v>130830.96</v>
@@ -11252,7 +11261,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B21" s="25" t="n">
         <v>557894.52</v>
@@ -11300,7 +11309,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B22" s="25" t="n">
         <v>145531.14</v>
@@ -11348,7 +11357,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B23" s="25" t="n">
         <v>70906.6</v>
@@ -11396,7 +11405,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B24" s="25" t="n">
         <v>5772.86</v>
@@ -11426,7 +11435,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="43" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B25" s="44" t="n">
         <f aca="false">SUM(B15:B24)</f>
@@ -11468,12 +11477,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -11491,25 +11500,25 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11658,12 +11667,12 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -11681,24 +11690,24 @@
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B42" s="23" t="n">
         <v>1</v>
@@ -11716,7 +11725,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B43" s="23" t="n">
         <v>8</v>
@@ -11734,7 +11743,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B44" s="23" t="n">
         <v>11</v>
@@ -11752,7 +11761,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B45" s="23" t="n">
         <v>13</v>
@@ -11770,7 +11779,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B46" s="23" t="n">
         <v>3</v>
@@ -11788,7 +11797,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="43" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B47" s="54"/>
       <c r="C47" s="44" t="n">
@@ -11803,12 +11812,12 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
@@ -11826,24 +11835,24 @@
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="16" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B53" s="36" t="n">
         <f aca="false">C10</f>
@@ -11864,7 +11873,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B54" s="36" t="n">
         <f aca="false">B25</f>
@@ -11885,7 +11894,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B55" s="36" t="n">
         <f aca="false">C25</f>
@@ -11906,7 +11915,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B56" s="36" t="n">
         <f aca="false">C47</f>
@@ -11927,7 +11936,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B57" s="36" t="n">
         <f aca="false">J25</f>
@@ -11948,15 +11957,15 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B58" s="36" t="n">
         <f aca="false">SUM('New Store'!$D$52:$BK$52)</f>
-        <v>3112214.36721807</v>
+        <v>6153321.55082711</v>
       </c>
       <c r="C58" s="36" t="n">
         <f aca="false">SUM('New Store'!B29:F29)</f>
-        <v>3112214.36721807</v>
+        <v>6153321.55082711</v>
       </c>
       <c r="D58" s="36" t="n">
         <f aca="false">B58-C58</f>
@@ -11969,15 +11978,15 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B59" s="36" t="n">
         <f aca="false">Cash!T28</f>
-        <v>-1134848.27174883</v>
+        <v>-651098.271748835</v>
       </c>
       <c r="C59" s="36" t="n">
         <f aca="false">cash_open+SUM(Cash!H27:T27)</f>
-        <v>-1134848.27174883</v>
+        <v>-651098.271748835</v>
       </c>
       <c r="D59" s="36" t="n">
         <f aca="false">B59-C59</f>
@@ -11990,7 +11999,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B60" s="36" t="n">
         <f aca="false">Inventory!B19</f>
@@ -12011,7 +12020,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B61" s="36" t="n">
         <f aca="false">SUM(Pricing!B28:F28)</f>
@@ -12031,7 +12040,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E62" s="98" t="str">
         <f aca="false">IF(ISNUMBER(MATCH(scenario,Inputs!$D$6:$F$6,0)),"OK","CHECK")</f>
@@ -12040,7 +12049,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="12" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E63" s="98" t="str">
         <f aca="false">IF(AND(ramp_start&gt;0,ramp_start&lt;=1,ramp_months&gt;=1,labor_floor&gt;=0,labor_floor&lt;=1),"OK","CHECK")</f>
@@ -12049,7 +12058,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E64" s="98" t="str">
         <f aca="false">IF(AND(MIN(E42:E46)&gt;=0,MAX(E42:E46)&lt;=6),"OK","CHECK")</f>
@@ -12058,7 +12067,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="12" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E65" s="98" t="str">
         <f aca="false">IF(ABS(D47-1)&lt;0.0001,"OK","CHECK")</f>
@@ -12067,7 +12076,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E66" s="98" t="str">
         <f aca="false">IF(ISNUMBER(MATCH(category,category_list,0)),"OK","CHECK")</f>
@@ -12076,7 +12085,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B68" s="3" t="str">
         <f aca="false">IF(COUNTIF(E53:E66,"OK")=ROWS(E53:E66),"All "&amp;ROWS(E53:E66)&amp;" checks pass",ROWS(E53:E66)-COUNTIF(E53:E66,"OK")&amp;" of "&amp;ROWS(E53:E66)&amp;" checks need a look")</f>
